--- a/research/traditional_assets/database/data/austria/austria_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_environmental_waste_services.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.006403162055335968</v>
+        <v>0.02803418803418803</v>
       </c>
       <c r="H2">
-        <v>0.006403162055335968</v>
+        <v>0.02803418803418803</v>
       </c>
       <c r="I2">
-        <v>-0.06245059288537549</v>
+        <v>-0.005025641025641026</v>
       </c>
       <c r="J2">
-        <v>-0.06245059288537549</v>
+        <v>-0.005025641025641026</v>
       </c>
       <c r="K2">
-        <v>-4.06</v>
+        <v>-2.12</v>
       </c>
       <c r="L2">
-        <v>-0.08023715415019762</v>
+        <v>-0.03623931623931624</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.77</v>
+        <v>6.06</v>
       </c>
       <c r="V2">
-        <v>0.087010078387458</v>
+        <v>0.09558359621451104</v>
       </c>
       <c r="W2">
-        <v>-0.4993849938499384</v>
+        <v>-0.2277121374865736</v>
       </c>
       <c r="X2">
-        <v>0.06140790093197943</v>
+        <v>0.1077878748977459</v>
       </c>
       <c r="Y2">
-        <v>-0.5607928947819179</v>
+        <v>-0.3355000123843195</v>
       </c>
       <c r="Z2">
-        <v>2.543991955756661</v>
+        <v>3.519855595667869</v>
       </c>
       <c r="AA2">
-        <v>-0.1588738059326294</v>
+        <v>-0.01768953068592057</v>
       </c>
       <c r="AB2">
-        <v>0.05419177845893925</v>
+        <v>0.09590167477403033</v>
       </c>
       <c r="AC2">
-        <v>-0.2130655843915687</v>
+        <v>-0.1135912054599509</v>
       </c>
       <c r="AD2">
-        <v>21</v>
+        <v>13.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21</v>
+        <v>13.4</v>
       </c>
       <c r="AG2">
-        <v>13.23</v>
+        <v>7.340000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1903898458748867</v>
+        <v>0.1744791666666667</v>
       </c>
       <c r="AI2">
-        <v>0.6521739130434782</v>
+        <v>0.458904109589041</v>
       </c>
       <c r="AJ2">
-        <v>0.1290354042719204</v>
+        <v>0.1037602487984167</v>
       </c>
       <c r="AK2">
-        <v>0.5415472779369628</v>
+        <v>0.317199654278306</v>
       </c>
       <c r="AL2">
-        <v>0.989</v>
+        <v>1.18</v>
       </c>
       <c r="AM2">
-        <v>0.982</v>
+        <v>1.171</v>
       </c>
       <c r="AN2">
-        <v>-38.32116788321168</v>
+        <v>4.060606060606061</v>
       </c>
       <c r="AO2">
-        <v>-3.195146612740142</v>
+        <v>-0.2491525423728813</v>
       </c>
       <c r="AP2">
-        <v>-24.14233576642336</v>
+        <v>2.224242424242425</v>
       </c>
       <c r="AQ2">
-        <v>-3.217922606924644</v>
+        <v>-0.251067463706234</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wolftank-Adisa Holding AG (MUN:WAH)</t>
+          <t>Wolftank-Adisa Holding AG (XTRA:WAH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.006403162055335968</v>
+        <v>0.02803418803418803</v>
       </c>
       <c r="H3">
-        <v>0.006403162055335968</v>
+        <v>0.02803418803418803</v>
       </c>
       <c r="I3">
-        <v>-0.06245059288537549</v>
+        <v>-0.005025641025641026</v>
       </c>
       <c r="J3">
-        <v>-0.06245059288537549</v>
+        <v>-0.005025641025641026</v>
       </c>
       <c r="K3">
-        <v>-4.06</v>
+        <v>-2.12</v>
       </c>
       <c r="L3">
-        <v>-0.08023715415019762</v>
+        <v>-0.03623931623931624</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.77</v>
+        <v>6.06</v>
       </c>
       <c r="V3">
-        <v>0.087010078387458</v>
+        <v>0.09558359621451104</v>
       </c>
       <c r="W3">
-        <v>-0.4993849938499384</v>
+        <v>-0.2277121374865736</v>
       </c>
       <c r="X3">
-        <v>0.06140790093197943</v>
+        <v>0.1077878748977459</v>
       </c>
       <c r="Y3">
-        <v>-0.5607928947819179</v>
+        <v>-0.3355000123843195</v>
       </c>
       <c r="Z3">
-        <v>2.543991955756661</v>
+        <v>3.519855595667869</v>
       </c>
       <c r="AA3">
-        <v>-0.1588738059326294</v>
+        <v>-0.01768953068592057</v>
       </c>
       <c r="AB3">
-        <v>0.05419177845893925</v>
+        <v>0.09590167477403033</v>
       </c>
       <c r="AC3">
-        <v>-0.2130655843915687</v>
+        <v>-0.1135912054599509</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>13.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>13.4</v>
       </c>
       <c r="AG3">
-        <v>13.23</v>
+        <v>7.340000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1903898458748867</v>
+        <v>0.1744791666666667</v>
       </c>
       <c r="AI3">
-        <v>0.6521739130434782</v>
+        <v>0.458904109589041</v>
       </c>
       <c r="AJ3">
-        <v>0.1290354042719204</v>
+        <v>0.1037602487984167</v>
       </c>
       <c r="AK3">
-        <v>0.5415472779369628</v>
+        <v>0.317199654278306</v>
       </c>
       <c r="AL3">
-        <v>0.989</v>
+        <v>1.18</v>
       </c>
       <c r="AM3">
-        <v>0.982</v>
+        <v>1.171</v>
       </c>
       <c r="AN3">
-        <v>-38.32116788321168</v>
+        <v>4.060606060606061</v>
       </c>
       <c r="AO3">
-        <v>-3.195146612740142</v>
+        <v>-0.2491525423728813</v>
       </c>
       <c r="AP3">
-        <v>-24.14233576642336</v>
+        <v>2.224242424242425</v>
       </c>
       <c r="AQ3">
-        <v>-3.217922606924644</v>
+        <v>-0.251067463706234</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/austria/austria_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_environmental_waste_services.xlsx
@@ -588,112 +588,115 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.02803418803418803</v>
+        <v>0.0538135593220339</v>
       </c>
       <c r="H2">
-        <v>0.02803418803418803</v>
+        <v>0.0538135593220339</v>
       </c>
       <c r="I2">
-        <v>-0.005025641025641026</v>
+        <v>-0.00480225988700565</v>
       </c>
       <c r="J2">
-        <v>-0.005025641025641026</v>
+        <v>-0.00480225988700565</v>
       </c>
       <c r="K2">
-        <v>-2.12</v>
+        <v>-2.68</v>
       </c>
       <c r="L2">
-        <v>-0.03623931623931624</v>
+        <v>-0.03785310734463277</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.232</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.09393177737881508</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-1.952238805970149</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>5.232</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.09393177737881508</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>-1.952238805970149</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>6.06</v>
+        <v>9.35</v>
       </c>
       <c r="V2">
-        <v>0.09558359621451104</v>
+        <v>0.1678635547576302</v>
       </c>
       <c r="W2">
-        <v>-0.2277121374865736</v>
+        <v>-0.2</v>
       </c>
       <c r="X2">
-        <v>0.1077878748977459</v>
+        <v>0.08777810481839676</v>
       </c>
       <c r="Y2">
-        <v>-0.3355000123843195</v>
+        <v>-0.2877781048183968</v>
       </c>
       <c r="Z2">
-        <v>3.519855595667869</v>
+        <v>5.152838427947597</v>
       </c>
       <c r="AA2">
-        <v>-0.01768953068592057</v>
+        <v>-0.024745269286754</v>
       </c>
       <c r="AB2">
-        <v>0.09590167477403033</v>
+        <v>0.07839079962199021</v>
       </c>
       <c r="AC2">
-        <v>-0.1135912054599509</v>
+        <v>-0.1031360689087442</v>
       </c>
       <c r="AD2">
-        <v>13.4</v>
+        <v>12.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13.4</v>
+        <v>12.8</v>
       </c>
       <c r="AG2">
-        <v>7.340000000000001</v>
+        <v>3.450000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1744791666666667</v>
+        <v>0.1868613138686132</v>
       </c>
       <c r="AI2">
-        <v>0.458904109589041</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="AJ2">
-        <v>0.1037602487984167</v>
+        <v>0.05832628909551988</v>
       </c>
       <c r="AK2">
-        <v>0.317199654278306</v>
+        <v>0.1422680412371135</v>
       </c>
       <c r="AL2">
-        <v>1.18</v>
+        <v>0.926</v>
       </c>
       <c r="AM2">
-        <v>1.171</v>
+        <v>0.9</v>
       </c>
       <c r="AN2">
-        <v>4.060606060606061</v>
+        <v>3.535911602209945</v>
       </c>
       <c r="AO2">
-        <v>-0.2491525423728813</v>
+        <v>-0.367170626349892</v>
       </c>
       <c r="AP2">
-        <v>2.224242424242425</v>
+        <v>0.9530386740331495</v>
       </c>
       <c r="AQ2">
-        <v>-0.251067463706234</v>
+        <v>-0.3777777777777778</v>
       </c>
     </row>
     <row r="3">
@@ -713,112 +716,115 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.02803418803418803</v>
+        <v>0.0538135593220339</v>
       </c>
       <c r="H3">
-        <v>0.02803418803418803</v>
+        <v>0.0538135593220339</v>
       </c>
       <c r="I3">
-        <v>-0.005025641025641026</v>
+        <v>-0.00480225988700565</v>
       </c>
       <c r="J3">
-        <v>-0.005025641025641026</v>
+        <v>-0.00480225988700565</v>
       </c>
       <c r="K3">
-        <v>-2.12</v>
+        <v>-2.68</v>
       </c>
       <c r="L3">
-        <v>-0.03623931623931624</v>
+        <v>-0.03785310734463277</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>5.232</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.09393177737881508</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-1.952238805970149</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>5.232</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.09393177737881508</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-1.952238805970149</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>6.06</v>
+        <v>9.35</v>
       </c>
       <c r="V3">
-        <v>0.09558359621451104</v>
+        <v>0.1678635547576302</v>
       </c>
       <c r="W3">
-        <v>-0.2277121374865736</v>
+        <v>-0.2</v>
       </c>
       <c r="X3">
-        <v>0.1077878748977459</v>
+        <v>0.08777810481839676</v>
       </c>
       <c r="Y3">
-        <v>-0.3355000123843195</v>
+        <v>-0.2877781048183968</v>
       </c>
       <c r="Z3">
-        <v>3.519855595667869</v>
+        <v>5.152838427947597</v>
       </c>
       <c r="AA3">
-        <v>-0.01768953068592057</v>
+        <v>-0.024745269286754</v>
       </c>
       <c r="AB3">
-        <v>0.09590167477403033</v>
+        <v>0.07839079962199021</v>
       </c>
       <c r="AC3">
-        <v>-0.1135912054599509</v>
+        <v>-0.1031360689087442</v>
       </c>
       <c r="AD3">
-        <v>13.4</v>
+        <v>12.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13.4</v>
+        <v>12.8</v>
       </c>
       <c r="AG3">
-        <v>7.340000000000001</v>
+        <v>3.450000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1744791666666667</v>
+        <v>0.1868613138686132</v>
       </c>
       <c r="AI3">
-        <v>0.458904109589041</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="AJ3">
-        <v>0.1037602487984167</v>
+        <v>0.05832628909551988</v>
       </c>
       <c r="AK3">
-        <v>0.317199654278306</v>
+        <v>0.1422680412371135</v>
       </c>
       <c r="AL3">
-        <v>1.18</v>
+        <v>0.926</v>
       </c>
       <c r="AM3">
-        <v>1.171</v>
+        <v>0.9</v>
       </c>
       <c r="AN3">
-        <v>4.060606060606061</v>
+        <v>3.535911602209945</v>
       </c>
       <c r="AO3">
-        <v>-0.2491525423728813</v>
+        <v>-0.367170626349892</v>
       </c>
       <c r="AP3">
-        <v>2.224242424242425</v>
+        <v>0.9530386740331495</v>
       </c>
       <c r="AQ3">
-        <v>-0.251067463706234</v>
+        <v>-0.3777777777777778</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/austria/austria_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_environmental_waste_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08491531812526182</v>
+        <v>0.08474572136176119</v>
       </c>
       <c r="C2">
-        <v>74.48972450255027</v>
+        <v>73.79417985132949</v>
       </c>
       <c r="D2">
-        <v>60.78972450255028</v>
+        <v>60.85617985132949</v>
       </c>
       <c r="E2">
-        <v>-31.9</v>
+        <v>-31.138</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="G2">
         <v>13.7</v>
@@ -1439,28 +1439,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0383286</v>
       </c>
       <c r="N2">
-        <v>7.149999999999999</v>
+        <v>7.111671399999999</v>
       </c>
       <c r="O2">
-        <v>1.716</v>
+        <v>1.706801136</v>
       </c>
       <c r="P2">
-        <v>5.433999999999999</v>
+        <v>5.404870263999999</v>
       </c>
       <c r="Q2">
-        <v>12.284</v>
+        <v>12.254870264</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08491531812526182</v>
+        <v>0.08521559733511232</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410373</v>
+        <v>0.8104261668449079</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>186.5447733546229</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08474572136176119</v>
+        <v>0.08457612459826055</v>
       </c>
       <c r="C3">
-        <v>73.79417985132949</v>
+        <v>73.09878065714496</v>
       </c>
       <c r="D3">
-        <v>60.85617985132949</v>
+        <v>60.92278065714496</v>
       </c>
       <c r="E3">
-        <v>-31.138</v>
+        <v>-30.376</v>
       </c>
       <c r="F3">
-        <v>0.762</v>
+        <v>1.524</v>
       </c>
       <c r="G3">
         <v>13.7</v>
@@ -1521,28 +1521,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M3">
-        <v>0.0383286</v>
+        <v>0.07665719999999999</v>
       </c>
       <c r="N3">
-        <v>7.111671399999999</v>
+        <v>7.073342799999999</v>
       </c>
       <c r="O3">
-        <v>1.706801136</v>
+        <v>1.697602272</v>
       </c>
       <c r="P3">
-        <v>5.404870263999999</v>
+        <v>5.375740528</v>
       </c>
       <c r="Q3">
-        <v>12.254870264</v>
+        <v>12.225740528</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08521559733511232</v>
+        <v>0.08552200469210261</v>
       </c>
       <c r="T3">
-        <v>0.8104261668449079</v>
+        <v>0.8167262246039595</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>186.5447733546229</v>
+        <v>93.27238667731145</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08457612459826055</v>
+        <v>0.08440652783475994</v>
       </c>
       <c r="C4">
-        <v>73.09878065714496</v>
+        <v>72.40352739808301</v>
       </c>
       <c r="D4">
-        <v>60.92278065714496</v>
+        <v>60.98952739808302</v>
       </c>
       <c r="E4">
-        <v>-30.376</v>
+        <v>-29.614</v>
       </c>
       <c r="F4">
-        <v>1.524</v>
+        <v>2.286</v>
       </c>
       <c r="G4">
         <v>13.7</v>
@@ -1603,28 +1603,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M4">
-        <v>0.07665719999999999</v>
+        <v>0.1149858</v>
       </c>
       <c r="N4">
-        <v>7.073342799999999</v>
+        <v>7.035014199999998</v>
       </c>
       <c r="O4">
-        <v>1.697602272</v>
+        <v>1.688403407999999</v>
       </c>
       <c r="P4">
-        <v>5.375740528</v>
+        <v>5.346610791999999</v>
       </c>
       <c r="Q4">
-        <v>12.225740528</v>
+        <v>12.196610792</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08552200469210261</v>
+        <v>0.08583472972655665</v>
       </c>
       <c r="T4">
-        <v>0.8167262246039595</v>
+        <v>0.8231561804611359</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>93.27238667731145</v>
+        <v>62.18159111820763</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08440652783475994</v>
+        <v>0.08423693107125931</v>
       </c>
       <c r="C5">
-        <v>72.40352739808301</v>
+        <v>71.70842055432747</v>
       </c>
       <c r="D5">
-        <v>60.98952739808302</v>
+        <v>61.05642055432748</v>
       </c>
       <c r="E5">
-        <v>-29.614</v>
+        <v>-28.852</v>
       </c>
       <c r="F5">
-        <v>2.286</v>
+        <v>3.048</v>
       </c>
       <c r="G5">
         <v>13.7</v>
@@ -1685,28 +1685,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M5">
-        <v>0.1149858</v>
+        <v>0.1533144</v>
       </c>
       <c r="N5">
-        <v>7.035014199999998</v>
+        <v>6.996685599999998</v>
       </c>
       <c r="O5">
-        <v>1.688403407999999</v>
+        <v>1.679204544</v>
       </c>
       <c r="P5">
-        <v>5.346610791999999</v>
+        <v>5.317481055999998</v>
       </c>
       <c r="Q5">
-        <v>12.196610792</v>
+        <v>12.167481056</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08583472972655665</v>
+        <v>0.08615396986589512</v>
       </c>
       <c r="T5">
-        <v>0.8231561804611359</v>
+        <v>0.8297200937320035</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.18159111820763</v>
+        <v>46.63619333865572</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08423693107125931</v>
+        <v>0.08406733430775869</v>
       </c>
       <c r="C6">
-        <v>71.70842055432747</v>
+        <v>71.01346060817109</v>
       </c>
       <c r="D6">
-        <v>61.05642055432748</v>
+        <v>61.12346060817109</v>
       </c>
       <c r="E6">
-        <v>-28.852</v>
+        <v>-28.09</v>
       </c>
       <c r="F6">
-        <v>3.048</v>
+        <v>3.81</v>
       </c>
       <c r="G6">
         <v>13.7</v>
@@ -1767,28 +1767,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M6">
-        <v>0.1533144</v>
+        <v>0.191643</v>
       </c>
       <c r="N6">
-        <v>6.996685599999998</v>
+        <v>6.958356999999999</v>
       </c>
       <c r="O6">
-        <v>1.679204544</v>
+        <v>1.67000568</v>
       </c>
       <c r="P6">
-        <v>5.317481055999998</v>
+        <v>5.288351319999999</v>
       </c>
       <c r="Q6">
-        <v>12.167481056</v>
+        <v>12.13835132</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08615396986589512</v>
+        <v>0.08647993085027231</v>
       </c>
       <c r="T6">
-        <v>0.8297200937320035</v>
+        <v>0.8364221946506788</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.63619333865572</v>
+        <v>37.30895467092458</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08406733430775869</v>
+        <v>0.08389773754425807</v>
       </c>
       <c r="C7">
-        <v>71.01346060817109</v>
+        <v>70.3186480440272</v>
       </c>
       <c r="D7">
-        <v>61.12346060817109</v>
+        <v>61.1906480440272</v>
       </c>
       <c r="E7">
-        <v>-28.09</v>
+        <v>-27.328</v>
       </c>
       <c r="F7">
-        <v>3.81</v>
+        <v>4.572000000000001</v>
       </c>
       <c r="G7">
         <v>13.7</v>
@@ -1849,28 +1849,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M7">
-        <v>0.191643</v>
+        <v>0.2299716</v>
       </c>
       <c r="N7">
-        <v>6.958356999999999</v>
+        <v>6.920028399999999</v>
       </c>
       <c r="O7">
-        <v>1.67000568</v>
+        <v>1.660806816</v>
       </c>
       <c r="P7">
-        <v>5.288351319999999</v>
+        <v>5.259221583999999</v>
       </c>
       <c r="Q7">
-        <v>12.13835132</v>
+        <v>12.109221584</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08647993085027231</v>
+        <v>0.08681282717474262</v>
       </c>
       <c r="T7">
-        <v>0.8364221946506788</v>
+        <v>0.8432668934612408</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.30895467092458</v>
+        <v>31.09079555910381</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08389773754425807</v>
+        <v>0.08372814078075744</v>
       </c>
       <c r="C8">
-        <v>70.3186480440272</v>
+        <v>69.62398334844136</v>
       </c>
       <c r="D8">
-        <v>61.1906480440272</v>
+        <v>61.25798334844136</v>
       </c>
       <c r="E8">
-        <v>-27.328</v>
+        <v>-26.566</v>
       </c>
       <c r="F8">
-        <v>4.572</v>
+        <v>5.334</v>
       </c>
       <c r="G8">
         <v>13.7</v>
@@ -1931,28 +1931,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M8">
-        <v>0.2299716</v>
+        <v>0.2683002</v>
       </c>
       <c r="N8">
-        <v>6.920028399999999</v>
+        <v>6.881699799999999</v>
       </c>
       <c r="O8">
-        <v>1.660806816</v>
+        <v>1.651607952</v>
       </c>
       <c r="P8">
-        <v>5.259221583999999</v>
+        <v>5.230091847999999</v>
       </c>
       <c r="Q8">
-        <v>12.109221584</v>
+        <v>12.080091848</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08681282717474262</v>
+        <v>0.08715288255995422</v>
       </c>
       <c r="T8">
-        <v>0.8432668934612408</v>
+        <v>0.8502587900956858</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.09079555910381</v>
+        <v>26.6492533363747</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08372814078075742</v>
+        <v>0.08355854401725681</v>
       </c>
       <c r="C9">
-        <v>69.62398334844136</v>
+        <v>68.9294670101031</v>
       </c>
       <c r="D9">
-        <v>61.25798334844136</v>
+        <v>61.3254670101031</v>
       </c>
       <c r="E9">
-        <v>-26.566</v>
+        <v>-25.804</v>
       </c>
       <c r="F9">
-        <v>5.334000000000001</v>
+        <v>6.096</v>
       </c>
       <c r="G9">
         <v>13.7</v>
@@ -2013,28 +2013,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M9">
-        <v>0.2683002</v>
+        <v>0.3066288</v>
       </c>
       <c r="N9">
-        <v>6.881699799999999</v>
+        <v>6.843371199999998</v>
       </c>
       <c r="O9">
-        <v>1.651607952</v>
+        <v>1.642409088</v>
       </c>
       <c r="P9">
-        <v>5.230091847999999</v>
+        <v>5.200962111999999</v>
       </c>
       <c r="Q9">
-        <v>12.080091848</v>
+        <v>12.050962112</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08715288255995422</v>
+        <v>0.08750033045354</v>
       </c>
       <c r="T9">
-        <v>0.8502587900956858</v>
+        <v>0.8574026844830536</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.6492533363747</v>
+        <v>23.31809666932786</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08355854401725681</v>
+        <v>0.08338894725375617</v>
       </c>
       <c r="C10">
-        <v>68.9294670101031</v>
+        <v>68.23509951985774</v>
       </c>
       <c r="D10">
-        <v>61.3254670101031</v>
+        <v>61.39309951985775</v>
       </c>
       <c r="E10">
-        <v>-25.804</v>
+        <v>-25.042</v>
       </c>
       <c r="F10">
-        <v>6.096</v>
+        <v>6.858</v>
       </c>
       <c r="G10">
         <v>13.7</v>
@@ -2095,28 +2095,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M10">
-        <v>0.3066288</v>
+        <v>0.3449574</v>
       </c>
       <c r="N10">
-        <v>6.843371199999998</v>
+        <v>6.805042599999998</v>
       </c>
       <c r="O10">
-        <v>1.642409088</v>
+        <v>1.633210223999999</v>
       </c>
       <c r="P10">
-        <v>5.200962111999999</v>
+        <v>5.171832375999999</v>
       </c>
       <c r="Q10">
-        <v>12.050962112</v>
+        <v>12.021832376</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08750033045354</v>
+        <v>0.08785541456456722</v>
       </c>
       <c r="T10">
-        <v>0.8574026844830536</v>
+        <v>0.8647035875382756</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.31809666932786</v>
+        <v>20.72719703940254</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08338894725375617</v>
+        <v>0.08321935049025554</v>
       </c>
       <c r="C11">
-        <v>68.23509951985774</v>
+        <v>67.54088137071832</v>
       </c>
       <c r="D11">
-        <v>61.39309951985775</v>
+        <v>61.46088137071833</v>
       </c>
       <c r="E11">
-        <v>-25.042</v>
+        <v>-24.28</v>
       </c>
       <c r="F11">
-        <v>6.858</v>
+        <v>7.619999999999999</v>
       </c>
       <c r="G11">
         <v>13.7</v>
@@ -2177,28 +2177,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M11">
-        <v>0.3449574</v>
+        <v>0.383286</v>
       </c>
       <c r="N11">
-        <v>6.805042599999998</v>
+        <v>6.766713999999999</v>
       </c>
       <c r="O11">
-        <v>1.633210223999999</v>
+        <v>1.62401136</v>
       </c>
       <c r="P11">
-        <v>5.171832375999999</v>
+        <v>5.142702639999999</v>
       </c>
       <c r="Q11">
-        <v>12.021832376</v>
+        <v>11.99270264</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08785541456456722</v>
+        <v>0.08821838943361726</v>
       </c>
       <c r="T11">
-        <v>0.8647035875382756</v>
+        <v>0.8721667328836138</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.72719703940254</v>
+        <v>18.65447733546229</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08321935049025554</v>
+        <v>0.08304975372675492</v>
       </c>
       <c r="C12">
-        <v>67.54088137071832</v>
+        <v>66.84681305787754</v>
       </c>
       <c r="D12">
-        <v>61.46088137071833</v>
+        <v>61.52881305787754</v>
       </c>
       <c r="E12">
-        <v>-24.28</v>
+        <v>-23.518</v>
       </c>
       <c r="F12">
-        <v>7.620000000000001</v>
+        <v>8.382</v>
       </c>
       <c r="G12">
         <v>13.7</v>
@@ -2259,28 +2259,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M12">
-        <v>0.383286</v>
+        <v>0.4216146</v>
       </c>
       <c r="N12">
-        <v>6.766713999999999</v>
+        <v>6.728385399999999</v>
       </c>
       <c r="O12">
-        <v>1.62401136</v>
+        <v>1.614812496</v>
       </c>
       <c r="P12">
-        <v>5.142702639999999</v>
+        <v>5.113572903999999</v>
       </c>
       <c r="Q12">
-        <v>11.99270264</v>
+        <v>11.963572904</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08821838943361726</v>
+        <v>0.08858952104129766</v>
       </c>
       <c r="T12">
-        <v>0.8721667328836138</v>
+        <v>0.8797975893603078</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.65447733546229</v>
+        <v>16.95861575951118</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08304975372675492</v>
+        <v>0.08288015696325428</v>
       </c>
       <c r="C13">
-        <v>66.84681305787754</v>
+        <v>66.15289507871982</v>
       </c>
       <c r="D13">
-        <v>61.52881305787754</v>
+        <v>61.59689507871983</v>
       </c>
       <c r="E13">
-        <v>-23.518</v>
+        <v>-22.756</v>
       </c>
       <c r="F13">
-        <v>8.382</v>
+        <v>9.144</v>
       </c>
       <c r="G13">
         <v>13.7</v>
@@ -2341,28 +2341,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M13">
-        <v>0.4216146</v>
+        <v>0.4599432</v>
       </c>
       <c r="N13">
-        <v>6.728385399999999</v>
+        <v>6.690056799999999</v>
       </c>
       <c r="O13">
-        <v>1.614812496</v>
+        <v>1.605613632</v>
       </c>
       <c r="P13">
-        <v>5.113572903999999</v>
+        <v>5.084443167999999</v>
       </c>
       <c r="Q13">
-        <v>11.963572904</v>
+        <v>11.934443168</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08858952104129766</v>
+        <v>0.0889690874582435</v>
       </c>
       <c r="T13">
-        <v>0.8797975893603078</v>
+        <v>0.8876018743932901</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.95861575951118</v>
+        <v>15.54539777955191</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08288015696325428</v>
+        <v>0.08271056019975366</v>
       </c>
       <c r="C14">
-        <v>66.15289507871982</v>
+        <v>65.4591279328335</v>
       </c>
       <c r="D14">
-        <v>61.59689507871983</v>
+        <v>61.66512793283351</v>
       </c>
       <c r="E14">
-        <v>-22.756</v>
+        <v>-21.994</v>
       </c>
       <c r="F14">
-        <v>9.144</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="G14">
         <v>13.7</v>
@@ -2423,28 +2423,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M14">
-        <v>0.4599432</v>
+        <v>0.4982718</v>
       </c>
       <c r="N14">
-        <v>6.690056799999999</v>
+        <v>6.651728199999998</v>
       </c>
       <c r="O14">
-        <v>1.605613632</v>
+        <v>1.596414768</v>
       </c>
       <c r="P14">
-        <v>5.084443167999999</v>
+        <v>5.055313431999998</v>
       </c>
       <c r="Q14">
-        <v>11.934443168</v>
+        <v>11.905313432</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0889690874582435</v>
+        <v>0.08935737953994674</v>
       </c>
       <c r="T14">
-        <v>0.8876018743932901</v>
+        <v>0.8955855682776057</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.54539777955191</v>
+        <v>14.34959795035561</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08271056019975366</v>
+        <v>0.08254096343625303</v>
       </c>
       <c r="C15">
-        <v>65.4591279328335</v>
+        <v>64.76551212202297</v>
       </c>
       <c r="D15">
-        <v>61.66512793283351</v>
+        <v>61.73351212202297</v>
       </c>
       <c r="E15">
-        <v>-21.994</v>
+        <v>-21.232</v>
       </c>
       <c r="F15">
-        <v>9.906000000000001</v>
+        <v>10.668</v>
       </c>
       <c r="G15">
         <v>13.7</v>
@@ -2505,28 +2505,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M15">
-        <v>0.4982718</v>
+        <v>0.5366004</v>
       </c>
       <c r="N15">
-        <v>6.651728199999998</v>
+        <v>6.613399599999998</v>
       </c>
       <c r="O15">
-        <v>1.596414768</v>
+        <v>1.587215904</v>
       </c>
       <c r="P15">
-        <v>5.055313431999998</v>
+        <v>5.026183695999999</v>
       </c>
       <c r="Q15">
-        <v>11.905313432</v>
+        <v>11.876183696</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08935737953994674</v>
+        <v>0.08975470167006167</v>
       </c>
       <c r="T15">
-        <v>0.8955855682776057</v>
+        <v>0.9037549294615563</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.34959795035561</v>
+        <v>13.32462666818735</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08254096343625303</v>
+        <v>0.0825423666727524</v>
       </c>
       <c r="C16">
-        <v>64.76551212202297</v>
+        <v>64.00294569185192</v>
       </c>
       <c r="D16">
-        <v>61.73351212202297</v>
+        <v>61.73294569185192</v>
       </c>
       <c r="E16">
-        <v>-21.232</v>
+        <v>-20.47</v>
       </c>
       <c r="F16">
-        <v>10.668</v>
+        <v>11.43</v>
       </c>
       <c r="G16">
         <v>13.7</v>
@@ -2587,45 +2587,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M16">
-        <v>0.5366004</v>
+        <v>0.5920740000000001</v>
       </c>
       <c r="N16">
-        <v>6.613399599999998</v>
+        <v>6.557925999999998</v>
       </c>
       <c r="O16">
-        <v>1.587215904</v>
+        <v>1.57390224</v>
       </c>
       <c r="P16">
-        <v>5.026183695999999</v>
+        <v>4.984023759999999</v>
       </c>
       <c r="Q16">
-        <v>11.876183696</v>
+        <v>11.83402376</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08975470167006167</v>
+        <v>0.0901613725561793</v>
       </c>
       <c r="T16">
-        <v>0.9037549294615563</v>
+        <v>0.9121165109086589</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.24</v>
       </c>
       <c r="W16">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.32462666818735</v>
+        <v>12.07619317855538</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08254236667275239</v>
+        <v>0.08238416990925176</v>
       </c>
       <c r="C17">
-        <v>64.00294569185192</v>
+        <v>63.30486890328176</v>
       </c>
       <c r="D17">
-        <v>61.73294569185193</v>
+        <v>61.79686890328177</v>
       </c>
       <c r="E17">
-        <v>-20.47</v>
+        <v>-19.708</v>
       </c>
       <c r="F17">
-        <v>11.43</v>
+        <v>12.192</v>
       </c>
       <c r="G17">
         <v>13.7</v>
@@ -2669,28 +2669,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M17">
-        <v>0.592074</v>
+        <v>0.6315456</v>
       </c>
       <c r="N17">
-        <v>6.557925999999998</v>
+        <v>6.518454399999999</v>
       </c>
       <c r="O17">
-        <v>1.57390224</v>
+        <v>1.564429056</v>
       </c>
       <c r="P17">
-        <v>4.984023759999999</v>
+        <v>4.954025343999999</v>
       </c>
       <c r="Q17">
-        <v>11.83402376</v>
+        <v>11.804025344</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09016137255617929</v>
+        <v>0.09057772608244259</v>
       </c>
       <c r="T17">
-        <v>0.9121165109086586</v>
+        <v>0.9206771776283114</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.07619317855538</v>
+        <v>11.32143110489567</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08238416990925176</v>
+        <v>0.08222597314575114</v>
       </c>
       <c r="C18">
-        <v>63.30486890328176</v>
+        <v>62.60692463430718</v>
       </c>
       <c r="D18">
-        <v>61.79686890328177</v>
+        <v>61.86092463430719</v>
       </c>
       <c r="E18">
-        <v>-19.708</v>
+        <v>-18.946</v>
       </c>
       <c r="F18">
-        <v>12.192</v>
+        <v>12.954</v>
       </c>
       <c r="G18">
         <v>13.7</v>
@@ -2751,28 +2751,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M18">
-        <v>0.6315456</v>
+        <v>0.6710172</v>
       </c>
       <c r="N18">
-        <v>6.518454399999999</v>
+        <v>6.478982799999999</v>
       </c>
       <c r="O18">
-        <v>1.564429056</v>
+        <v>1.554955872</v>
       </c>
       <c r="P18">
-        <v>4.954025343999999</v>
+        <v>4.924026927999999</v>
       </c>
       <c r="Q18">
-        <v>11.804025344</v>
+        <v>11.774026928</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09057772608244259</v>
+        <v>0.09100411222379656</v>
       </c>
       <c r="T18">
-        <v>0.9206771776283114</v>
+        <v>0.9294441254737386</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.32143110489567</v>
+        <v>10.65546456931357</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08222597314575114</v>
+        <v>0.08206777638225052</v>
       </c>
       <c r="C19">
-        <v>62.60692463430718</v>
+        <v>61.90911329744655</v>
       </c>
       <c r="D19">
-        <v>61.86092463430719</v>
+        <v>61.92511329744654</v>
       </c>
       <c r="E19">
-        <v>-18.946</v>
+        <v>-18.184</v>
       </c>
       <c r="F19">
-        <v>12.954</v>
+        <v>13.716</v>
       </c>
       <c r="G19">
         <v>13.7</v>
@@ -2833,28 +2833,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M19">
-        <v>0.6710172</v>
+        <v>0.7104888000000001</v>
       </c>
       <c r="N19">
-        <v>6.478982799999999</v>
+        <v>6.439511199999998</v>
       </c>
       <c r="O19">
-        <v>1.554955872</v>
+        <v>1.545482687999999</v>
       </c>
       <c r="P19">
-        <v>4.924026927999999</v>
+        <v>4.894028511999998</v>
       </c>
       <c r="Q19">
-        <v>11.774026928</v>
+        <v>11.744028512</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09100411222379656</v>
+        <v>0.09144089802713479</v>
       </c>
       <c r="T19">
-        <v>0.9294441254737386</v>
+        <v>0.9384249013153958</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.65546456931357</v>
+        <v>10.06349431546282</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0820677763822505</v>
+        <v>0.08215505961874989</v>
       </c>
       <c r="C20">
-        <v>61.90911329744655</v>
+        <v>61.11168148089509</v>
       </c>
       <c r="D20">
-        <v>61.92511329744655</v>
+        <v>61.8896814808951</v>
       </c>
       <c r="E20">
-        <v>-18.184</v>
+        <v>-17.422</v>
       </c>
       <c r="F20">
-        <v>13.716</v>
+        <v>14.478</v>
       </c>
       <c r="G20">
         <v>13.7</v>
@@ -2915,45 +2915,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M20">
-        <v>0.7104887999999999</v>
+        <v>0.7745730000000001</v>
       </c>
       <c r="N20">
-        <v>6.439511199999998</v>
+        <v>6.375426999999998</v>
       </c>
       <c r="O20">
-        <v>1.545482687999999</v>
+        <v>1.53010248</v>
       </c>
       <c r="P20">
-        <v>4.894028511999998</v>
+        <v>4.845324519999998</v>
       </c>
       <c r="Q20">
-        <v>11.744028512</v>
+        <v>11.69532452</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09144089802713476</v>
+        <v>0.09188846866512332</v>
       </c>
       <c r="T20">
-        <v>0.9384249013153956</v>
+        <v>0.9476274247086987</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.06349431546282</v>
+        <v>9.230892375541101</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08215505961874989</v>
+        <v>0.08200978285524925</v>
       </c>
       <c r="C21">
-        <v>61.11168148089509</v>
+        <v>60.40867767063869</v>
       </c>
       <c r="D21">
-        <v>61.8896814808951</v>
+        <v>61.94867767063869</v>
       </c>
       <c r="E21">
-        <v>-17.422</v>
+        <v>-16.66</v>
       </c>
       <c r="F21">
-        <v>14.478</v>
+        <v>15.24</v>
       </c>
       <c r="G21">
         <v>13.7</v>
@@ -2997,28 +2997,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M21">
-        <v>0.7745730000000001</v>
+        <v>0.8153400000000001</v>
       </c>
       <c r="N21">
-        <v>6.375426999999998</v>
+        <v>6.334659999999999</v>
       </c>
       <c r="O21">
-        <v>1.53010248</v>
+        <v>1.5203184</v>
       </c>
       <c r="P21">
-        <v>4.845324519999998</v>
+        <v>4.814341599999999</v>
       </c>
       <c r="Q21">
-        <v>11.69532452</v>
+        <v>11.6643416</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09188846866512332</v>
+        <v>0.09234722856906157</v>
       </c>
       <c r="T21">
-        <v>0.9476274247086987</v>
+        <v>0.9570600111868343</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.230892375541101</v>
+        <v>8.769347756764047</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08200978285524925</v>
+        <v>0.08186450609174864</v>
       </c>
       <c r="C22">
-        <v>60.40867767063869</v>
+        <v>59.70578644365344</v>
       </c>
       <c r="D22">
-        <v>61.94867767063869</v>
+        <v>62.00778644365345</v>
       </c>
       <c r="E22">
-        <v>-16.66</v>
+        <v>-15.898</v>
       </c>
       <c r="F22">
-        <v>15.24</v>
+        <v>16.002</v>
       </c>
       <c r="G22">
         <v>13.7</v>
@@ -3079,28 +3079,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M22">
-        <v>0.8153400000000001</v>
+        <v>0.8561070000000001</v>
       </c>
       <c r="N22">
-        <v>6.334659999999999</v>
+        <v>6.293892999999999</v>
       </c>
       <c r="O22">
-        <v>1.5203184</v>
+        <v>1.51053432</v>
       </c>
       <c r="P22">
-        <v>4.814341599999999</v>
+        <v>4.783358679999999</v>
       </c>
       <c r="Q22">
-        <v>11.6643416</v>
+        <v>11.63335868</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09234722856906157</v>
+        <v>0.09281760264778308</v>
       </c>
       <c r="T22">
-        <v>0.9570600111868343</v>
+        <v>0.9667313973226443</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.769347756764047</v>
+        <v>8.351759768346712</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08186450609174864</v>
+        <v>0.081719229328248</v>
       </c>
       <c r="C23">
-        <v>59.70578644365345</v>
+        <v>59.00300812251358</v>
       </c>
       <c r="D23">
-        <v>62.00778644365345</v>
+        <v>62.06700812251357</v>
       </c>
       <c r="E23">
-        <v>-15.898</v>
+        <v>-15.136</v>
       </c>
       <c r="F23">
-        <v>16.002</v>
+        <v>16.764</v>
       </c>
       <c r="G23">
         <v>13.7</v>
@@ -3161,28 +3161,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M23">
-        <v>0.856107</v>
+        <v>0.8968739999999999</v>
       </c>
       <c r="N23">
-        <v>6.293892999999999</v>
+        <v>6.253125999999998</v>
       </c>
       <c r="O23">
-        <v>1.51053432</v>
+        <v>1.500750239999999</v>
       </c>
       <c r="P23">
-        <v>4.783358679999999</v>
+        <v>4.752375759999999</v>
       </c>
       <c r="Q23">
-        <v>11.63335868</v>
+        <v>11.60237576</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09281760264778308</v>
+        <v>0.09330003760031795</v>
       </c>
       <c r="T23">
-        <v>0.9667313973226443</v>
+        <v>0.9766507677183469</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.351759768346714</v>
+        <v>7.972134324330952</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.081719229328248</v>
+        <v>0.08157395256474737</v>
       </c>
       <c r="C24">
-        <v>59.00300812251358</v>
+        <v>58.30034303102671</v>
       </c>
       <c r="D24">
-        <v>62.06700812251357</v>
+        <v>62.12634303102671</v>
       </c>
       <c r="E24">
-        <v>-15.136</v>
+        <v>-14.374</v>
       </c>
       <c r="F24">
-        <v>16.764</v>
+        <v>17.526</v>
       </c>
       <c r="G24">
         <v>13.7</v>
@@ -3243,28 +3243,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M24">
-        <v>0.8968739999999999</v>
+        <v>0.9376409999999999</v>
       </c>
       <c r="N24">
-        <v>6.253125999999998</v>
+        <v>6.212358999999998</v>
       </c>
       <c r="O24">
-        <v>1.500750239999999</v>
+        <v>1.490966159999999</v>
       </c>
       <c r="P24">
-        <v>4.752375759999999</v>
+        <v>4.721392839999999</v>
       </c>
       <c r="Q24">
-        <v>11.60237576</v>
+        <v>11.57139284</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09330003760031795</v>
+        <v>0.09379500333084075</v>
       </c>
       <c r="T24">
-        <v>0.9766507677183469</v>
+        <v>0.9868277840983534</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.972134324330952</v>
+        <v>7.625519788490476</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08157395256474737</v>
+        <v>0.08157459580124676</v>
       </c>
       <c r="C25">
-        <v>58.30034303102671</v>
+        <v>57.53808006603099</v>
       </c>
       <c r="D25">
-        <v>62.12634303102671</v>
+        <v>62.12608006603099</v>
       </c>
       <c r="E25">
-        <v>-14.374</v>
+        <v>-13.612</v>
       </c>
       <c r="F25">
-        <v>17.526</v>
+        <v>18.288</v>
       </c>
       <c r="G25">
         <v>13.7</v>
@@ -3325,45 +3325,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M25">
-        <v>0.9376409999999999</v>
+        <v>0.9930384000000002</v>
       </c>
       <c r="N25">
-        <v>6.212358999999998</v>
+        <v>6.156961599999998</v>
       </c>
       <c r="O25">
-        <v>1.490966159999999</v>
+        <v>1.477670783999999</v>
       </c>
       <c r="P25">
-        <v>4.721392839999999</v>
+        <v>4.679290815999998</v>
       </c>
       <c r="Q25">
-        <v>11.57139284</v>
+        <v>11.529290816</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09379500333084075</v>
+        <v>0.09430299447532467</v>
       </c>
       <c r="T25">
-        <v>0.9868277840983534</v>
+        <v>0.9972726166988862</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.24</v>
       </c>
       <c r="W25">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.625519788490476</v>
+        <v>7.200124385925053</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08157459580124675</v>
+        <v>0.08143539903774613</v>
       </c>
       <c r="C26">
-        <v>57.538080066031</v>
+        <v>56.83303777912195</v>
       </c>
       <c r="D26">
-        <v>62.126080066031</v>
+        <v>62.18303777912195</v>
       </c>
       <c r="E26">
-        <v>-13.612</v>
+        <v>-12.85</v>
       </c>
       <c r="F26">
-        <v>18.288</v>
+        <v>19.05</v>
       </c>
       <c r="G26">
         <v>13.7</v>
@@ -3407,28 +3407,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M26">
-        <v>0.9930384</v>
+        <v>1.034415</v>
       </c>
       <c r="N26">
-        <v>6.156961599999999</v>
+        <v>6.115584999999998</v>
       </c>
       <c r="O26">
-        <v>1.477670784</v>
+        <v>1.4677404</v>
       </c>
       <c r="P26">
-        <v>4.679290815999999</v>
+        <v>4.647844599999999</v>
       </c>
       <c r="Q26">
-        <v>11.529290816</v>
+        <v>11.4978446</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09430299447532467</v>
+        <v>0.09482453205032816</v>
       </c>
       <c r="T26">
-        <v>0.9972726166988862</v>
+        <v>1.007995978168767</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.200124385925055</v>
+        <v>6.912119410488052</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08143539903774613</v>
+        <v>0.08129620227424549</v>
       </c>
       <c r="C27">
-        <v>56.83303777912195</v>
+        <v>56.12810002667248</v>
       </c>
       <c r="D27">
-        <v>62.18303777912195</v>
+        <v>62.24010002667248</v>
       </c>
       <c r="E27">
-        <v>-12.85</v>
+        <v>-12.088</v>
       </c>
       <c r="F27">
-        <v>19.05</v>
+        <v>19.812</v>
       </c>
       <c r="G27">
         <v>13.7</v>
@@ -3489,28 +3489,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M27">
-        <v>1.034415</v>
+        <v>1.0757916</v>
       </c>
       <c r="N27">
-        <v>6.115584999999998</v>
+        <v>6.074208399999998</v>
       </c>
       <c r="O27">
-        <v>1.4677404</v>
+        <v>1.457810015999999</v>
       </c>
       <c r="P27">
-        <v>4.647844599999999</v>
+        <v>4.616398383999998</v>
       </c>
       <c r="Q27">
-        <v>11.4978446</v>
+        <v>11.466398384</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09482453205032816</v>
+        <v>0.09536016523546686</v>
       </c>
       <c r="T27">
-        <v>1.007995978168767</v>
+        <v>1.019009160218914</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.912119410488052</v>
+        <v>6.646268663930819</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08129620227424549</v>
+        <v>0.08115700551074487</v>
       </c>
       <c r="C28">
-        <v>56.12810002667248</v>
+        <v>55.42326709672494</v>
       </c>
       <c r="D28">
-        <v>62.24010002667248</v>
+        <v>62.29726709672494</v>
       </c>
       <c r="E28">
-        <v>-12.088</v>
+        <v>-11.326</v>
       </c>
       <c r="F28">
-        <v>19.812</v>
+        <v>20.574</v>
       </c>
       <c r="G28">
         <v>13.7</v>
@@ -3571,28 +3571,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M28">
-        <v>1.0757916</v>
+        <v>1.1171682</v>
       </c>
       <c r="N28">
-        <v>6.074208399999998</v>
+        <v>6.032831799999999</v>
       </c>
       <c r="O28">
-        <v>1.457810015999999</v>
+        <v>1.447879632</v>
       </c>
       <c r="P28">
-        <v>4.616398383999998</v>
+        <v>4.584952167999999</v>
       </c>
       <c r="Q28">
-        <v>11.466398384</v>
+        <v>11.434952168</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09536016523546686</v>
+        <v>0.09591047330239022</v>
       </c>
       <c r="T28">
-        <v>1.019009160218914</v>
+        <v>1.030324073284134</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.646268663930819</v>
+        <v>6.400110565266715</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08115700551074487</v>
+        <v>0.08101780874724422</v>
       </c>
       <c r="C29">
-        <v>55.42326709672494</v>
+        <v>54.71853927838096</v>
       </c>
       <c r="D29">
-        <v>62.29726709672494</v>
+        <v>62.35453927838096</v>
       </c>
       <c r="E29">
-        <v>-11.326</v>
+        <v>-10.564</v>
       </c>
       <c r="F29">
-        <v>20.574</v>
+        <v>21.336</v>
       </c>
       <c r="G29">
         <v>13.7</v>
@@ -3653,28 +3653,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M29">
-        <v>1.1171682</v>
+        <v>1.1585448</v>
       </c>
       <c r="N29">
-        <v>6.032831799999999</v>
+        <v>5.991455199999999</v>
       </c>
       <c r="O29">
-        <v>1.447879632</v>
+        <v>1.437949248</v>
       </c>
       <c r="P29">
-        <v>4.584952167999999</v>
+        <v>4.553505951999999</v>
       </c>
       <c r="Q29">
-        <v>11.434952168</v>
+        <v>11.403505952</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09591047330239022</v>
+        <v>0.09647606770450587</v>
       </c>
       <c r="T29">
-        <v>1.030324073284134</v>
+        <v>1.041953289490055</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.400110565266715</v>
+        <v>6.171535187935761</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08101780874724422</v>
+        <v>0.0810990119837436</v>
       </c>
       <c r="C30">
-        <v>54.71853927838096</v>
+        <v>53.92311560701829</v>
       </c>
       <c r="D30">
-        <v>62.35453927838096</v>
+        <v>62.32111560701829</v>
       </c>
       <c r="E30">
-        <v>-10.564</v>
+        <v>-9.802</v>
       </c>
       <c r="F30">
-        <v>21.336</v>
+        <v>22.098</v>
       </c>
       <c r="G30">
         <v>13.7</v>
@@ -3735,45 +3735,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M30">
-        <v>1.1585448</v>
+        <v>1.2220194</v>
       </c>
       <c r="N30">
-        <v>5.991455199999999</v>
+        <v>5.927980599999998</v>
       </c>
       <c r="O30">
-        <v>1.437949248</v>
+        <v>1.422715344</v>
       </c>
       <c r="P30">
-        <v>4.553505951999999</v>
+        <v>4.505265255999999</v>
       </c>
       <c r="Q30">
-        <v>11.403505952</v>
+        <v>11.355265256</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09647606770450587</v>
+        <v>0.09705759434330086</v>
       </c>
       <c r="T30">
-        <v>1.041953289490055</v>
+        <v>1.053910089251072</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.171535187935761</v>
+        <v>5.850970942032506</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0810990119837436</v>
+        <v>0.08096741522024296</v>
       </c>
       <c r="C31">
-        <v>53.92311560701829</v>
+        <v>53.21529954820943</v>
       </c>
       <c r="D31">
-        <v>62.32111560701829</v>
+        <v>62.37529954820943</v>
       </c>
       <c r="E31">
-        <v>-9.802000000000003</v>
+        <v>-9.040000000000003</v>
       </c>
       <c r="F31">
-        <v>22.098</v>
+        <v>22.86</v>
       </c>
       <c r="G31">
         <v>13.7</v>
@@ -3817,28 +3817,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M31">
-        <v>1.2220194</v>
+        <v>1.264158</v>
       </c>
       <c r="N31">
-        <v>5.927980599999999</v>
+        <v>5.885841999999998</v>
       </c>
       <c r="O31">
-        <v>1.422715344</v>
+        <v>1.41260208</v>
       </c>
       <c r="P31">
-        <v>4.505265255999999</v>
+        <v>4.473239919999999</v>
       </c>
       <c r="Q31">
-        <v>11.355265256</v>
+        <v>11.32323992</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09705759434330086</v>
+        <v>0.09765573602891853</v>
       </c>
       <c r="T31">
-        <v>1.053910089251072</v>
+        <v>1.066208511862404</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.850970942032507</v>
+        <v>5.655938577298089</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08096741522024296</v>
+        <v>0.08083581845674234</v>
       </c>
       <c r="C32">
-        <v>53.21529954820943</v>
+        <v>52.50757778983913</v>
       </c>
       <c r="D32">
-        <v>62.37529954820943</v>
+        <v>62.42957778983914</v>
       </c>
       <c r="E32">
-        <v>-9.040000000000003</v>
+        <v>-8.278000000000002</v>
       </c>
       <c r="F32">
-        <v>22.86</v>
+        <v>23.622</v>
       </c>
       <c r="G32">
         <v>13.7</v>
@@ -3899,28 +3899,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M32">
-        <v>1.264158</v>
+        <v>1.3062966</v>
       </c>
       <c r="N32">
-        <v>5.885841999999998</v>
+        <v>5.843703399999999</v>
       </c>
       <c r="O32">
-        <v>1.41260208</v>
+        <v>1.402488816</v>
       </c>
       <c r="P32">
-        <v>4.473239919999999</v>
+        <v>4.441214583999999</v>
       </c>
       <c r="Q32">
-        <v>11.32323992</v>
+        <v>11.291214584</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09765573602891853</v>
+        <v>0.09827121515469905</v>
       </c>
       <c r="T32">
-        <v>1.066208511862404</v>
+        <v>1.078863410491455</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.655938577298089</v>
+        <v>5.473488945772345</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08083581845674234</v>
+        <v>0.08070422169324171</v>
       </c>
       <c r="C33">
-        <v>52.50757778983913</v>
+        <v>51.79995057829922</v>
       </c>
       <c r="D33">
-        <v>62.42957778983914</v>
+        <v>62.48395057829921</v>
       </c>
       <c r="E33">
-        <v>-8.278000000000002</v>
+        <v>-7.516000000000002</v>
       </c>
       <c r="F33">
-        <v>23.622</v>
+        <v>24.384</v>
       </c>
       <c r="G33">
         <v>13.7</v>
@@ -3981,28 +3981,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M33">
-        <v>1.3062966</v>
+        <v>1.3484352</v>
       </c>
       <c r="N33">
-        <v>5.843703399999999</v>
+        <v>5.801564799999999</v>
       </c>
       <c r="O33">
-        <v>1.402488816</v>
+        <v>1.392375552</v>
       </c>
       <c r="P33">
-        <v>4.441214583999999</v>
+        <v>4.409189247999999</v>
       </c>
       <c r="Q33">
-        <v>11.291214584</v>
+        <v>11.259189248</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09827121515469905</v>
+        <v>0.0989047966077084</v>
       </c>
       <c r="T33">
-        <v>1.078863410491455</v>
+        <v>1.091890512021361</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.473488945772345</v>
+        <v>5.302442416216959</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08070422169324171</v>
+        <v>0.08057262492974109</v>
       </c>
       <c r="C34">
-        <v>51.79995057829922</v>
+        <v>51.09241816084052</v>
       </c>
       <c r="D34">
-        <v>62.48395057829921</v>
+        <v>62.53841816084052</v>
       </c>
       <c r="E34">
-        <v>-7.516000000000002</v>
+        <v>-6.754000000000001</v>
       </c>
       <c r="F34">
-        <v>24.384</v>
+        <v>25.146</v>
       </c>
       <c r="G34">
         <v>13.7</v>
@@ -4063,28 +4063,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M34">
-        <v>1.3484352</v>
+        <v>1.3905738</v>
       </c>
       <c r="N34">
-        <v>5.801564799999999</v>
+        <v>5.759426199999998</v>
       </c>
       <c r="O34">
-        <v>1.392375552</v>
+        <v>1.382262288</v>
       </c>
       <c r="P34">
-        <v>4.409189247999999</v>
+        <v>4.377163911999999</v>
       </c>
       <c r="Q34">
-        <v>11.259189248</v>
+        <v>11.227163912</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0989047966077084</v>
+        <v>0.09955729093991207</v>
       </c>
       <c r="T34">
-        <v>1.091890512021361</v>
+        <v>1.105306482253652</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.302442416216959</v>
+        <v>5.141762342998263</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08057262492974109</v>
+        <v>0.08044102816624045</v>
       </c>
       <c r="C35">
-        <v>51.09241816084052</v>
+        <v>50.3849807855768</v>
       </c>
       <c r="D35">
-        <v>62.53841816084052</v>
+        <v>62.59298078557681</v>
       </c>
       <c r="E35">
-        <v>-6.754000000000001</v>
+        <v>-5.992000000000001</v>
       </c>
       <c r="F35">
-        <v>25.146</v>
+        <v>25.908</v>
       </c>
       <c r="G35">
         <v>13.7</v>
@@ -4145,28 +4145,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M35">
-        <v>1.3905738</v>
+        <v>1.4327124</v>
       </c>
       <c r="N35">
-        <v>5.759426199999998</v>
+        <v>5.717287599999999</v>
       </c>
       <c r="O35">
-        <v>1.382262288</v>
+        <v>1.372149024</v>
       </c>
       <c r="P35">
-        <v>4.377163911999999</v>
+        <v>4.345138575999999</v>
       </c>
       <c r="Q35">
-        <v>11.227163912</v>
+        <v>11.195138576</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09955729093991207</v>
+        <v>0.1002295578276371</v>
       </c>
       <c r="T35">
-        <v>1.105306482253652</v>
+        <v>1.119128997038437</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.141762342998263</v>
+        <v>4.990534038792432</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08044102816624045</v>
+        <v>0.08030943140273983</v>
       </c>
       <c r="C36">
-        <v>50.3849807855768</v>
+        <v>49.67763870148848</v>
       </c>
       <c r="D36">
-        <v>62.59298078557681</v>
+        <v>62.64763870148848</v>
       </c>
       <c r="E36">
-        <v>-5.992000000000001</v>
+        <v>-5.229999999999997</v>
       </c>
       <c r="F36">
-        <v>25.908</v>
+        <v>26.67000000000001</v>
       </c>
       <c r="G36">
         <v>13.7</v>
@@ -4227,28 +4227,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M36">
-        <v>1.4327124</v>
+        <v>1.474851</v>
       </c>
       <c r="N36">
-        <v>5.717287599999999</v>
+        <v>5.675148999999998</v>
       </c>
       <c r="O36">
-        <v>1.372149024</v>
+        <v>1.362035759999999</v>
       </c>
       <c r="P36">
-        <v>4.345138575999999</v>
+        <v>4.313113239999999</v>
       </c>
       <c r="Q36">
-        <v>11.195138576</v>
+        <v>11.16311324</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1002295578276371</v>
+        <v>0.100922509850369</v>
       </c>
       <c r="T36">
-        <v>1.119128997038437</v>
+        <v>1.133376819970446</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.990534038792432</v>
+        <v>4.84794735196979</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08030943140273983</v>
+        <v>0.08017783463923919</v>
       </c>
       <c r="C37">
-        <v>49.67763870148848</v>
+        <v>48.97039215842635</v>
       </c>
       <c r="D37">
-        <v>62.64763870148848</v>
+        <v>62.70239215842635</v>
       </c>
       <c r="E37">
-        <v>-5.229999999999997</v>
+        <v>-4.467999999999996</v>
       </c>
       <c r="F37">
-        <v>26.67000000000001</v>
+        <v>27.43200000000001</v>
       </c>
       <c r="G37">
         <v>13.7</v>
@@ -4309,28 +4309,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M37">
-        <v>1.474851</v>
+        <v>1.5169896</v>
       </c>
       <c r="N37">
-        <v>5.675148999999998</v>
+        <v>5.633010399999998</v>
       </c>
       <c r="O37">
-        <v>1.362035759999999</v>
+        <v>1.351922496</v>
       </c>
       <c r="P37">
-        <v>4.313113239999999</v>
+        <v>4.281087903999999</v>
       </c>
       <c r="Q37">
-        <v>11.16311324</v>
+        <v>11.131087904</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.100922509850369</v>
+        <v>0.1016371166238113</v>
       </c>
       <c r="T37">
-        <v>1.133376819970446</v>
+        <v>1.148069887369081</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.84794735196979</v>
+        <v>4.713282147748407</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08017783463923921</v>
+        <v>0.08004623787573857</v>
       </c>
       <c r="C38">
-        <v>48.97039215842634</v>
+        <v>48.26324140711546</v>
       </c>
       <c r="D38">
-        <v>62.70239215842633</v>
+        <v>62.75724140711546</v>
       </c>
       <c r="E38">
-        <v>-4.468000000000004</v>
+        <v>-3.706000000000003</v>
       </c>
       <c r="F38">
-        <v>27.432</v>
+        <v>28.194</v>
       </c>
       <c r="G38">
         <v>13.7</v>
@@ -4391,28 +4391,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M38">
-        <v>1.5169896</v>
+        <v>1.5591282</v>
       </c>
       <c r="N38">
-        <v>5.633010399999998</v>
+        <v>5.590871799999999</v>
       </c>
       <c r="O38">
-        <v>1.351922496</v>
+        <v>1.341809232</v>
       </c>
       <c r="P38">
-        <v>4.281087903999999</v>
+        <v>4.249062567999999</v>
       </c>
       <c r="Q38">
-        <v>11.131087904</v>
+        <v>11.099062568</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1016371166238113</v>
+        <v>0.1023744093265692</v>
       </c>
       <c r="T38">
-        <v>1.148069887369081</v>
+        <v>1.163229401351799</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.713282147748408</v>
+        <v>4.585896143755209</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08004623787573857</v>
+        <v>0.08063664111223795</v>
       </c>
       <c r="C39">
-        <v>48.26324140711546</v>
+        <v>47.2559101613535</v>
       </c>
       <c r="D39">
-        <v>62.75724140711546</v>
+        <v>62.51191016135351</v>
       </c>
       <c r="E39">
-        <v>-3.706000000000003</v>
+        <v>-2.943999999999999</v>
       </c>
       <c r="F39">
-        <v>28.194</v>
+        <v>28.956</v>
       </c>
       <c r="G39">
         <v>13.7</v>
@@ -4473,45 +4473,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M39">
-        <v>1.5591282</v>
+        <v>1.6736568</v>
       </c>
       <c r="N39">
-        <v>5.590871799999999</v>
+        <v>5.476343199999999</v>
       </c>
       <c r="O39">
-        <v>1.341809232</v>
+        <v>1.314322368</v>
       </c>
       <c r="P39">
-        <v>4.249062567999999</v>
+        <v>4.162020832</v>
       </c>
       <c r="Q39">
-        <v>11.099062568</v>
+        <v>11.012020832</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1023744093265692</v>
+        <v>0.1031354856648999</v>
       </c>
       <c r="T39">
-        <v>1.163229401351799</v>
+        <v>1.178877931914604</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.24</v>
       </c>
       <c r="W39">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.585896143755209</v>
+        <v>4.272082544043676</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08063664111223795</v>
+        <v>0.08052404434873731</v>
       </c>
       <c r="C40">
-        <v>47.2559101613535</v>
+        <v>46.54054955198094</v>
       </c>
       <c r="D40">
-        <v>62.51191016135351</v>
+        <v>62.55854955198095</v>
       </c>
       <c r="E40">
-        <v>-2.943999999999999</v>
+        <v>-2.181999999999999</v>
       </c>
       <c r="F40">
-        <v>28.956</v>
+        <v>29.718</v>
       </c>
       <c r="G40">
         <v>13.7</v>
@@ -4555,28 +4555,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M40">
-        <v>1.6736568</v>
+        <v>1.7177004</v>
       </c>
       <c r="N40">
-        <v>5.476343199999999</v>
+        <v>5.432299599999999</v>
       </c>
       <c r="O40">
-        <v>1.314322368</v>
+        <v>1.303751904</v>
       </c>
       <c r="P40">
-        <v>4.162020832</v>
+        <v>4.128547695999999</v>
       </c>
       <c r="Q40">
-        <v>11.012020832</v>
+        <v>10.978547696</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1031354856648999</v>
+        <v>0.1039215153257989</v>
       </c>
       <c r="T40">
-        <v>1.178877931914604</v>
+        <v>1.19503952905324</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.272082544043676</v>
+        <v>4.162541965991274</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08052404434873731</v>
+        <v>0.08041144758523669</v>
       </c>
       <c r="C41">
-        <v>46.54054955198094</v>
+        <v>45.82525858875675</v>
       </c>
       <c r="D41">
-        <v>62.55854955198095</v>
+        <v>62.60525858875676</v>
       </c>
       <c r="E41">
-        <v>-2.181999999999999</v>
+        <v>-1.419999999999998</v>
       </c>
       <c r="F41">
-        <v>29.718</v>
+        <v>30.48</v>
       </c>
       <c r="G41">
         <v>13.7</v>
@@ -4637,28 +4637,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M41">
-        <v>1.7177004</v>
+        <v>1.761744</v>
       </c>
       <c r="N41">
-        <v>5.432299599999999</v>
+        <v>5.388255999999998</v>
       </c>
       <c r="O41">
-        <v>1.303751904</v>
+        <v>1.293181439999999</v>
       </c>
       <c r="P41">
-        <v>4.128547695999999</v>
+        <v>4.095074559999999</v>
       </c>
       <c r="Q41">
-        <v>10.978547696</v>
+        <v>10.94507456</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1039215153257989</v>
+        <v>0.1047337459753945</v>
       </c>
       <c r="T41">
-        <v>1.19503952905324</v>
+        <v>1.211739846096496</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.162541965991274</v>
+        <v>4.058478416841492</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08041144758523669</v>
+        <v>0.08138945082173606</v>
       </c>
       <c r="C42">
-        <v>45.82525858875675</v>
+        <v>44.65986219439351</v>
       </c>
       <c r="D42">
-        <v>62.60525858875676</v>
+        <v>62.20186219439351</v>
       </c>
       <c r="E42">
-        <v>-1.419999999999998</v>
+        <v>-0.6579999999999977</v>
       </c>
       <c r="F42">
-        <v>30.48</v>
+        <v>31.242</v>
       </c>
       <c r="G42">
         <v>13.7</v>
@@ -4719,45 +4719,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M42">
-        <v>1.761744</v>
+        <v>1.9151346</v>
       </c>
       <c r="N42">
-        <v>5.388255999999998</v>
+        <v>5.234865399999999</v>
       </c>
       <c r="O42">
-        <v>1.293181439999999</v>
+        <v>1.256367696</v>
       </c>
       <c r="P42">
-        <v>4.095074559999999</v>
+        <v>3.978497703999999</v>
       </c>
       <c r="Q42">
-        <v>10.94507456</v>
+        <v>10.828497704</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1047337459753945</v>
+        <v>0.1055735098673493</v>
       </c>
       <c r="T42">
-        <v>1.211739846096496</v>
+        <v>1.229006275581897</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.24</v>
       </c>
       <c r="W42">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.058478416841492</v>
+        <v>3.733419050546107</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08138945082173606</v>
+        <v>0.08130345405823544</v>
       </c>
       <c r="C43">
-        <v>44.65986219439351</v>
+        <v>43.93312464844418</v>
       </c>
       <c r="D43">
-        <v>62.20186219439351</v>
+        <v>62.23712464844419</v>
       </c>
       <c r="E43">
-        <v>-0.6579999999999977</v>
+        <v>0.1040000000000028</v>
       </c>
       <c r="F43">
-        <v>31.242</v>
+        <v>32.004</v>
       </c>
       <c r="G43">
         <v>13.7</v>
@@ -4801,28 +4801,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M43">
-        <v>1.9151346</v>
+        <v>1.9618452</v>
       </c>
       <c r="N43">
-        <v>5.234865399999999</v>
+        <v>5.188154799999998</v>
       </c>
       <c r="O43">
-        <v>1.256367696</v>
+        <v>1.245157151999999</v>
       </c>
       <c r="P43">
-        <v>3.978497703999999</v>
+        <v>3.942997647999999</v>
       </c>
       <c r="Q43">
-        <v>10.828497704</v>
+        <v>10.792997648</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1055735098673493</v>
+        <v>0.1064422311348887</v>
       </c>
       <c r="T43">
-        <v>1.229006275581897</v>
+        <v>1.246868099187484</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.733419050546107</v>
+        <v>3.644528120771199</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08130345405823543</v>
+        <v>0.08121745729473481</v>
       </c>
       <c r="C44">
-        <v>43.9331246484442</v>
+        <v>43.20642710599099</v>
       </c>
       <c r="D44">
-        <v>62.23712464844419</v>
+        <v>62.27242710599099</v>
       </c>
       <c r="E44">
-        <v>0.1039999999999957</v>
+        <v>0.8659999999999961</v>
       </c>
       <c r="F44">
-        <v>32.004</v>
+        <v>32.766</v>
       </c>
       <c r="G44">
         <v>13.7</v>
@@ -4883,28 +4883,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M44">
-        <v>1.9618452</v>
+        <v>2.0085558</v>
       </c>
       <c r="N44">
-        <v>5.188154799999999</v>
+        <v>5.141444199999999</v>
       </c>
       <c r="O44">
-        <v>1.245157152</v>
+        <v>1.233946608</v>
       </c>
       <c r="P44">
-        <v>3.942997647999999</v>
+        <v>3.907497591999999</v>
       </c>
       <c r="Q44">
-        <v>10.792997648</v>
+        <v>10.757497592</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1064422311348887</v>
+        <v>0.1073414338504119</v>
       </c>
       <c r="T44">
-        <v>1.246868099187484</v>
+        <v>1.265356653445899</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.6445281207712</v>
+        <v>3.559771652846288</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08121745729473481</v>
+        <v>0.08206778053123417</v>
       </c>
       <c r="C45">
-        <v>43.20642710599099</v>
+        <v>42.0971116122411</v>
       </c>
       <c r="D45">
-        <v>62.27242710599099</v>
+        <v>61.9251116122411</v>
       </c>
       <c r="E45">
-        <v>0.8659999999999961</v>
+        <v>1.627999999999997</v>
       </c>
       <c r="F45">
-        <v>32.766</v>
+        <v>33.528</v>
       </c>
       <c r="G45">
         <v>13.7</v>
@@ -4965,45 +4965,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M45">
-        <v>2.0085558</v>
+        <v>2.1491448</v>
       </c>
       <c r="N45">
-        <v>5.141444199999999</v>
+        <v>5.000855199999998</v>
       </c>
       <c r="O45">
-        <v>1.233946608</v>
+        <v>1.200205248</v>
       </c>
       <c r="P45">
-        <v>3.907497591999999</v>
+        <v>3.800649951999999</v>
       </c>
       <c r="Q45">
-        <v>10.757497592</v>
+        <v>10.650649952</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1073414338504119</v>
+        <v>0.1082727509486325</v>
       </c>
       <c r="T45">
-        <v>1.265356653445899</v>
+        <v>1.284505513213542</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.24</v>
       </c>
       <c r="W45">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.559771652846288</v>
+        <v>3.326904729732496</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08206778053123417</v>
+        <v>0.08200306376773356</v>
       </c>
       <c r="C46">
-        <v>42.0971116122411</v>
+        <v>41.36140898096125</v>
       </c>
       <c r="D46">
-        <v>61.9251116122411</v>
+        <v>61.95140898096125</v>
       </c>
       <c r="E46">
-        <v>1.627999999999997</v>
+        <v>2.389999999999997</v>
       </c>
       <c r="F46">
-        <v>33.528</v>
+        <v>34.29</v>
       </c>
       <c r="G46">
         <v>13.7</v>
@@ -5047,28 +5047,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M46">
-        <v>2.1491448</v>
+        <v>2.197989</v>
       </c>
       <c r="N46">
-        <v>5.000855199999998</v>
+        <v>4.952010999999999</v>
       </c>
       <c r="O46">
-        <v>1.200205248</v>
+        <v>1.18848264</v>
       </c>
       <c r="P46">
-        <v>3.800649951999999</v>
+        <v>3.763528359999999</v>
       </c>
       <c r="Q46">
-        <v>10.650649952</v>
+        <v>10.61352836</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1082727509486325</v>
+        <v>0.1092379341231519</v>
       </c>
       <c r="T46">
-        <v>1.284505513213542</v>
+        <v>1.304350695154555</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.326904729732496</v>
+        <v>3.252973513516218</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08200306376773356</v>
+        <v>0.08193834700423291</v>
       </c>
       <c r="C47">
-        <v>41.36140898096125</v>
+        <v>40.62572869426459</v>
       </c>
       <c r="D47">
-        <v>61.95140898096125</v>
+        <v>61.97772869426459</v>
       </c>
       <c r="E47">
-        <v>2.389999999999997</v>
+        <v>3.151999999999997</v>
       </c>
       <c r="F47">
-        <v>34.29</v>
+        <v>35.052</v>
       </c>
       <c r="G47">
         <v>13.7</v>
@@ -5129,28 +5129,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M47">
-        <v>2.197989</v>
+        <v>2.2468332</v>
       </c>
       <c r="N47">
-        <v>4.952010999999999</v>
+        <v>4.903166799999998</v>
       </c>
       <c r="O47">
-        <v>1.18848264</v>
+        <v>1.176760032</v>
       </c>
       <c r="P47">
-        <v>3.763528359999999</v>
+        <v>3.726406767999999</v>
       </c>
       <c r="Q47">
-        <v>10.61352836</v>
+        <v>10.576406768</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1092379341231519</v>
+        <v>0.1102388648226535</v>
       </c>
       <c r="T47">
-        <v>1.304350695154555</v>
+        <v>1.324930883834124</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.252973513516218</v>
+        <v>3.182256698004996</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08193834700423291</v>
+        <v>0.08187363024073228</v>
       </c>
       <c r="C48">
-        <v>40.62572869426459</v>
+        <v>39.89007078064211</v>
       </c>
       <c r="D48">
-        <v>61.97772869426459</v>
+        <v>62.00407078064212</v>
       </c>
       <c r="E48">
-        <v>3.151999999999997</v>
+        <v>3.913999999999998</v>
       </c>
       <c r="F48">
-        <v>35.052</v>
+        <v>35.814</v>
       </c>
       <c r="G48">
         <v>13.7</v>
@@ -5211,28 +5211,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M48">
-        <v>2.2468332</v>
+        <v>2.2956774</v>
       </c>
       <c r="N48">
-        <v>4.903166799999998</v>
+        <v>4.854322599999998</v>
       </c>
       <c r="O48">
-        <v>1.176760032</v>
+        <v>1.165037423999999</v>
       </c>
       <c r="P48">
-        <v>3.726406767999999</v>
+        <v>3.689285175999999</v>
       </c>
       <c r="Q48">
-        <v>10.576406768</v>
+        <v>10.539285176</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1102388648226535</v>
+        <v>0.1112775664919477</v>
       </c>
       <c r="T48">
-        <v>1.324930883834124</v>
+        <v>1.346287683407261</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.182256698004996</v>
+        <v>3.11454910868574</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08187363024073228</v>
+        <v>0.08180891347723167</v>
       </c>
       <c r="C49">
-        <v>39.89007078064211</v>
+        <v>39.15443526863331</v>
       </c>
       <c r="D49">
-        <v>62.00407078064212</v>
+        <v>62.03043526863331</v>
       </c>
       <c r="E49">
-        <v>3.913999999999998</v>
+        <v>4.676000000000005</v>
       </c>
       <c r="F49">
-        <v>35.814</v>
+        <v>36.57600000000001</v>
       </c>
       <c r="G49">
         <v>13.7</v>
@@ -5293,28 +5293,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M49">
-        <v>2.2956774</v>
+        <v>2.344521600000001</v>
       </c>
       <c r="N49">
-        <v>4.854322599999998</v>
+        <v>4.805478399999998</v>
       </c>
       <c r="O49">
-        <v>1.165037423999999</v>
+        <v>1.153314816</v>
       </c>
       <c r="P49">
-        <v>3.689285175999999</v>
+        <v>3.652163583999999</v>
       </c>
       <c r="Q49">
-        <v>10.539285176</v>
+        <v>10.502163584</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1112775664919477</v>
+        <v>0.1123562182254455</v>
       </c>
       <c r="T49">
-        <v>1.346287683407261</v>
+        <v>1.368465898348596</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.11454910868574</v>
+        <v>3.049662668921454</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08180891347723167</v>
+        <v>0.08464891671373104</v>
       </c>
       <c r="C50">
-        <v>39.15443526863331</v>
+        <v>37.25617727784989</v>
       </c>
       <c r="D50">
-        <v>62.03043526863331</v>
+        <v>60.89417727784989</v>
       </c>
       <c r="E50">
-        <v>4.675999999999998</v>
+        <v>5.437999999999999</v>
       </c>
       <c r="F50">
-        <v>36.576</v>
+        <v>37.338</v>
       </c>
       <c r="G50">
         <v>13.7</v>
@@ -5375,45 +5375,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M50">
-        <v>2.3445216</v>
+        <v>2.6846022</v>
       </c>
       <c r="N50">
-        <v>4.805478399999998</v>
+        <v>4.465397799999998</v>
       </c>
       <c r="O50">
-        <v>1.153314816</v>
+        <v>1.071695472</v>
       </c>
       <c r="P50">
-        <v>3.652163583999999</v>
+        <v>3.393702327999998</v>
       </c>
       <c r="Q50">
-        <v>10.502163584</v>
+        <v>10.243702328</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1123562182254455</v>
+        <v>0.1134771700269236</v>
       </c>
       <c r="T50">
-        <v>1.368465898348596</v>
+        <v>1.391513847209198</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.24</v>
       </c>
       <c r="W50">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.049662668921454</v>
+        <v>2.663336862347799</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08464891671373104</v>
+        <v>0.0846434799502304</v>
       </c>
       <c r="C51">
-        <v>37.25617727784989</v>
+        <v>36.49631270482816</v>
       </c>
       <c r="D51">
-        <v>60.89417727784989</v>
+        <v>60.89631270482816</v>
       </c>
       <c r="E51">
-        <v>5.437999999999999</v>
+        <v>6.199999999999999</v>
       </c>
       <c r="F51">
-        <v>37.338</v>
+        <v>38.1</v>
       </c>
       <c r="G51">
         <v>13.7</v>
@@ -5457,28 +5457,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M51">
-        <v>2.6846022</v>
+        <v>2.73939</v>
       </c>
       <c r="N51">
-        <v>4.465397799999998</v>
+        <v>4.410609999999998</v>
       </c>
       <c r="O51">
-        <v>1.071695472</v>
+        <v>1.0585464</v>
       </c>
       <c r="P51">
-        <v>3.393702327999998</v>
+        <v>3.352063599999999</v>
       </c>
       <c r="Q51">
-        <v>10.243702328</v>
+        <v>10.2020636</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1134771700269236</v>
+        <v>0.1146429599004608</v>
       </c>
       <c r="T51">
-        <v>1.391513847209198</v>
+        <v>1.415483714024226</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.663336862347799</v>
+        <v>2.610070125100843</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0846434799502304</v>
+        <v>0.08463804318672978</v>
       </c>
       <c r="C52">
-        <v>36.49631270482816</v>
+        <v>35.7364482815813</v>
       </c>
       <c r="D52">
-        <v>60.89631270482816</v>
+        <v>60.8984482815813</v>
       </c>
       <c r="E52">
-        <v>6.199999999999999</v>
+        <v>6.962</v>
       </c>
       <c r="F52">
-        <v>38.1</v>
+        <v>38.862</v>
       </c>
       <c r="G52">
         <v>13.7</v>
@@ -5539,28 +5539,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M52">
-        <v>2.73939</v>
+        <v>2.7941778</v>
       </c>
       <c r="N52">
-        <v>4.410609999999998</v>
+        <v>4.355822199999999</v>
       </c>
       <c r="O52">
-        <v>1.0585464</v>
+        <v>1.045397328</v>
       </c>
       <c r="P52">
-        <v>3.352063599999999</v>
+        <v>3.310424871999999</v>
       </c>
       <c r="Q52">
-        <v>10.2020636</v>
+        <v>10.160424872</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1146429599004608</v>
+        <v>0.1158563330341424</v>
       </c>
       <c r="T52">
-        <v>1.415483714024226</v>
+        <v>1.44043194275007</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.610070125100843</v>
+        <v>2.55889227951063</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08463804318672978</v>
+        <v>0.08463260642322915</v>
       </c>
       <c r="C53">
-        <v>35.7364482815813</v>
+        <v>34.97658400812504</v>
       </c>
       <c r="D53">
-        <v>60.8984482815813</v>
+        <v>60.90058400812504</v>
       </c>
       <c r="E53">
-        <v>6.962</v>
+        <v>7.724</v>
       </c>
       <c r="F53">
-        <v>38.862</v>
+        <v>39.624</v>
       </c>
       <c r="G53">
         <v>13.7</v>
@@ -5621,28 +5621,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M53">
-        <v>2.7941778</v>
+        <v>2.848965600000001</v>
       </c>
       <c r="N53">
-        <v>4.355822199999999</v>
+        <v>4.301034399999998</v>
       </c>
       <c r="O53">
-        <v>1.045397328</v>
+        <v>1.032248255999999</v>
       </c>
       <c r="P53">
-        <v>3.310424871999999</v>
+        <v>3.268786143999999</v>
       </c>
       <c r="Q53">
-        <v>10.160424872</v>
+        <v>10.118786144</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1158563330341424</v>
+        <v>0.1171202633817274</v>
       </c>
       <c r="T53">
-        <v>1.44043194275007</v>
+        <v>1.466419681006158</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.55889227951063</v>
+        <v>2.509682812596964</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08463260642322915</v>
+        <v>0.08619808965972851</v>
       </c>
       <c r="C54">
-        <v>34.97658400812504</v>
+        <v>33.60574113846776</v>
       </c>
       <c r="D54">
-        <v>60.90058400812504</v>
+        <v>60.29174113846776</v>
       </c>
       <c r="E54">
-        <v>7.724</v>
+        <v>8.486000000000001</v>
       </c>
       <c r="F54">
-        <v>39.624</v>
+        <v>40.386</v>
       </c>
       <c r="G54">
         <v>13.7</v>
@@ -5703,45 +5703,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M54">
-        <v>2.848965600000001</v>
+        <v>3.061258800000001</v>
       </c>
       <c r="N54">
-        <v>4.301034399999998</v>
+        <v>4.088741199999998</v>
       </c>
       <c r="O54">
-        <v>1.032248255999999</v>
+        <v>0.9812978879999994</v>
       </c>
       <c r="P54">
-        <v>3.268786143999999</v>
+        <v>3.107443311999998</v>
       </c>
       <c r="Q54">
-        <v>10.118786144</v>
+        <v>9.957443311999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1171202633817274</v>
+        <v>0.1184379779994224</v>
       </c>
       <c r="T54">
-        <v>1.466419681006158</v>
+        <v>1.493513280464633</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.24</v>
       </c>
       <c r="W54">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.509682812596964</v>
+        <v>2.335640488808067</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08619808965972851</v>
+        <v>0.0862222928962279</v>
       </c>
       <c r="C55">
-        <v>33.60574113846776</v>
+        <v>32.83442363646868</v>
       </c>
       <c r="D55">
-        <v>60.29174113846776</v>
+        <v>60.28242363646868</v>
       </c>
       <c r="E55">
-        <v>8.486000000000001</v>
+        <v>9.248000000000001</v>
       </c>
       <c r="F55">
-        <v>40.386</v>
+        <v>41.148</v>
       </c>
       <c r="G55">
         <v>13.7</v>
@@ -5785,28 +5785,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M55">
-        <v>3.061258800000001</v>
+        <v>3.1190184</v>
       </c>
       <c r="N55">
-        <v>4.088741199999998</v>
+        <v>4.030981599999999</v>
       </c>
       <c r="O55">
-        <v>0.9812978879999994</v>
+        <v>0.9674355839999996</v>
       </c>
       <c r="P55">
-        <v>3.107443311999998</v>
+        <v>3.063546015999999</v>
       </c>
       <c r="Q55">
-        <v>9.957443311999999</v>
+        <v>9.913546015999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1184379779994224</v>
+        <v>0.1198129845570172</v>
       </c>
       <c r="T55">
-        <v>1.493513280464633</v>
+        <v>1.521784862508258</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.335640488808067</v>
+        <v>2.292387887163474</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0862222928962279</v>
+        <v>0.08624649613272727</v>
       </c>
       <c r="C56">
-        <v>32.83442363646868</v>
+        <v>32.06310901388317</v>
       </c>
       <c r="D56">
-        <v>60.28242363646868</v>
+        <v>60.27310901388318</v>
       </c>
       <c r="E56">
-        <v>9.248000000000001</v>
+        <v>10.01</v>
       </c>
       <c r="F56">
-        <v>41.148</v>
+        <v>41.91</v>
       </c>
       <c r="G56">
         <v>13.7</v>
@@ -5867,28 +5867,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M56">
-        <v>3.1190184</v>
+        <v>3.176778000000001</v>
       </c>
       <c r="N56">
-        <v>4.030981599999999</v>
+        <v>3.973221999999998</v>
       </c>
       <c r="O56">
-        <v>0.9674355839999996</v>
+        <v>0.9535732799999995</v>
       </c>
       <c r="P56">
-        <v>3.063546015999999</v>
+        <v>3.019648719999998</v>
       </c>
       <c r="Q56">
-        <v>9.913546015999998</v>
+        <v>9.869648719999997</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1198129845570172</v>
+        <v>0.1212491025171717</v>
       </c>
       <c r="T56">
-        <v>1.521784862508258</v>
+        <v>1.551312959309379</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.292387887163474</v>
+        <v>2.250708107396865</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08624649613272727</v>
+        <v>0.08627069936922663</v>
       </c>
       <c r="C57">
-        <v>32.06310901388317</v>
+        <v>31.29179726937671</v>
       </c>
       <c r="D57">
-        <v>60.27310901388318</v>
+        <v>60.26379726937671</v>
       </c>
       <c r="E57">
-        <v>10.01</v>
+        <v>10.772</v>
       </c>
       <c r="F57">
-        <v>41.91</v>
+        <v>42.672</v>
       </c>
       <c r="G57">
         <v>13.7</v>
@@ -5949,28 +5949,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M57">
-        <v>3.176778000000001</v>
+        <v>3.234537600000001</v>
       </c>
       <c r="N57">
-        <v>3.973221999999998</v>
+        <v>3.915462399999998</v>
       </c>
       <c r="O57">
-        <v>0.9535732799999995</v>
+        <v>0.9397109759999994</v>
       </c>
       <c r="P57">
-        <v>3.019648719999998</v>
+        <v>2.975751423999998</v>
       </c>
       <c r="Q57">
-        <v>9.869648719999997</v>
+        <v>9.825751423999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1212491025171717</v>
+        <v>0.1227504985664242</v>
       </c>
       <c r="T57">
-        <v>1.551312959309379</v>
+        <v>1.582183242328731</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.250708107396865</v>
+        <v>2.210516891193349</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08627069936922663</v>
+        <v>0.08629490260572602</v>
       </c>
       <c r="C58">
-        <v>31.29179726937671</v>
+        <v>30.52048840161554</v>
       </c>
       <c r="D58">
-        <v>60.26379726937671</v>
+        <v>60.25448840161555</v>
       </c>
       <c r="E58">
-        <v>10.772</v>
+        <v>11.534</v>
       </c>
       <c r="F58">
-        <v>42.672</v>
+        <v>43.434</v>
       </c>
       <c r="G58">
         <v>13.7</v>
@@ -6031,28 +6031,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M58">
-        <v>3.234537600000001</v>
+        <v>3.292297200000001</v>
       </c>
       <c r="N58">
-        <v>3.915462399999998</v>
+        <v>3.857702799999998</v>
       </c>
       <c r="O58">
-        <v>0.9397109759999994</v>
+        <v>0.9258486719999994</v>
       </c>
       <c r="P58">
-        <v>2.975751423999998</v>
+        <v>2.931854127999999</v>
       </c>
       <c r="Q58">
-        <v>9.825751423999998</v>
+        <v>9.781854127999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1227504985664242</v>
+        <v>0.1243217269900605</v>
       </c>
       <c r="T58">
-        <v>1.582183242328731</v>
+        <v>1.614489352465264</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.210516891193349</v>
+        <v>2.171735893102238</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08629490260572602</v>
+        <v>0.08631910584222538</v>
       </c>
       <c r="C59">
-        <v>30.52048840161554</v>
+        <v>29.74918240926682</v>
       </c>
       <c r="D59">
-        <v>60.25448840161555</v>
+        <v>60.24518240926682</v>
       </c>
       <c r="E59">
-        <v>11.534</v>
+        <v>12.296</v>
       </c>
       <c r="F59">
-        <v>43.434</v>
+        <v>44.19600000000001</v>
       </c>
       <c r="G59">
         <v>13.7</v>
@@ -6113,28 +6113,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M59">
-        <v>3.292297200000001</v>
+        <v>3.350056800000001</v>
       </c>
       <c r="N59">
-        <v>3.857702799999998</v>
+        <v>3.799943199999998</v>
       </c>
       <c r="O59">
-        <v>0.9258486719999994</v>
+        <v>0.9119863679999994</v>
       </c>
       <c r="P59">
-        <v>2.931854127999999</v>
+        <v>2.887956831999998</v>
       </c>
       <c r="Q59">
-        <v>9.781854127999999</v>
+        <v>9.737956831999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1243217269900605</v>
+        <v>0.1259677758148223</v>
       </c>
       <c r="T59">
-        <v>1.614489352465264</v>
+        <v>1.648333848798774</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.171735893102238</v>
+        <v>2.134292170807372</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08631910584222538</v>
+        <v>0.08634330907872476</v>
       </c>
       <c r="C60">
-        <v>29.74918240926682</v>
+        <v>28.97787929099843</v>
       </c>
       <c r="D60">
-        <v>60.24518240926682</v>
+        <v>60.23587929099843</v>
       </c>
       <c r="E60">
-        <v>12.296</v>
+        <v>13.058</v>
       </c>
       <c r="F60">
-        <v>44.196</v>
+        <v>44.958</v>
       </c>
       <c r="G60">
         <v>13.7</v>
@@ -6195,28 +6195,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M60">
-        <v>3.3500568</v>
+        <v>3.4078164</v>
       </c>
       <c r="N60">
-        <v>3.799943199999999</v>
+        <v>3.742183599999998</v>
       </c>
       <c r="O60">
-        <v>0.9119863679999997</v>
+        <v>0.8981240639999996</v>
       </c>
       <c r="P60">
-        <v>2.887956831999999</v>
+        <v>2.844059535999999</v>
       </c>
       <c r="Q60">
-        <v>9.737956831999998</v>
+        <v>9.694059535999997</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1259677758148223</v>
+        <v>0.1276941197042067</v>
       </c>
       <c r="T60">
-        <v>1.648333848798774</v>
+        <v>1.683829296172942</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.134292170807372</v>
+        <v>2.098117727234365</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08634330907872476</v>
+        <v>0.08636751231522413</v>
       </c>
       <c r="C61">
-        <v>28.97787929099843</v>
+        <v>28.20657904547913</v>
       </c>
       <c r="D61">
-        <v>60.23587929099843</v>
+        <v>60.22657904547913</v>
       </c>
       <c r="E61">
-        <v>13.058</v>
+        <v>13.82</v>
       </c>
       <c r="F61">
-        <v>44.958</v>
+        <v>45.72</v>
       </c>
       <c r="G61">
         <v>13.7</v>
@@ -6277,28 +6277,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M61">
-        <v>3.4078164</v>
+        <v>3.465576</v>
       </c>
       <c r="N61">
-        <v>3.742183599999998</v>
+        <v>3.684423999999999</v>
       </c>
       <c r="O61">
-        <v>0.8981240639999996</v>
+        <v>0.8842617599999997</v>
       </c>
       <c r="P61">
-        <v>2.844059535999999</v>
+        <v>2.800162239999999</v>
       </c>
       <c r="Q61">
-        <v>9.694059535999997</v>
+        <v>9.650162239999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1276941197042067</v>
+        <v>0.1295067807880603</v>
       </c>
       <c r="T61">
-        <v>1.683829296172942</v>
+        <v>1.72109951591582</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.098117727234365</v>
+        <v>2.063149098447126</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08636751231522413</v>
+        <v>0.08639171555172351</v>
       </c>
       <c r="C62">
-        <v>28.20657904547913</v>
+        <v>27.43528167137852</v>
       </c>
       <c r="D62">
-        <v>60.22657904547913</v>
+        <v>60.21728167137852</v>
       </c>
       <c r="E62">
-        <v>13.82</v>
+        <v>14.582</v>
       </c>
       <c r="F62">
-        <v>45.72</v>
+        <v>46.482</v>
       </c>
       <c r="G62">
         <v>13.7</v>
@@ -6359,28 +6359,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M62">
-        <v>3.465576</v>
+        <v>3.5233356</v>
       </c>
       <c r="N62">
-        <v>3.684423999999999</v>
+        <v>3.626664399999998</v>
       </c>
       <c r="O62">
-        <v>0.8842617599999997</v>
+        <v>0.8703994559999996</v>
       </c>
       <c r="P62">
-        <v>2.800162239999999</v>
+        <v>2.756264943999999</v>
       </c>
       <c r="Q62">
-        <v>9.650162239999998</v>
+        <v>9.606264943999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1295067807880603</v>
+        <v>0.1314123988505731</v>
       </c>
       <c r="T62">
-        <v>1.72109951591582</v>
+        <v>1.760281028978845</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.063149098447126</v>
+        <v>2.029326982079141</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08639171555172351</v>
+        <v>0.09310695878822287</v>
       </c>
       <c r="C63">
-        <v>27.43528167137852</v>
+        <v>24.20003440418061</v>
       </c>
       <c r="D63">
-        <v>60.21728167137852</v>
+        <v>57.74403440418061</v>
       </c>
       <c r="E63">
-        <v>14.582</v>
+        <v>15.344</v>
       </c>
       <c r="F63">
-        <v>46.482</v>
+        <v>47.244</v>
       </c>
       <c r="G63">
         <v>13.7</v>
@@ -6441,45 +6441,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M63">
-        <v>3.5233356</v>
+        <v>4.25196</v>
       </c>
       <c r="N63">
-        <v>3.626664399999998</v>
+        <v>2.898039999999999</v>
       </c>
       <c r="O63">
-        <v>0.8703994559999996</v>
+        <v>0.6955295999999997</v>
       </c>
       <c r="P63">
-        <v>2.756264943999999</v>
+        <v>2.2025104</v>
       </c>
       <c r="Q63">
-        <v>9.606264943999999</v>
+        <v>9.052510399999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1314123988505731</v>
+        <v>0.1334183126005865</v>
       </c>
       <c r="T63">
-        <v>1.760281028978845</v>
+        <v>1.801524726939924</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
         <v>0.24</v>
       </c>
       <c r="W63">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.029326982079141</v>
+        <v>1.681577437228948</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09310695878822287</v>
+        <v>0.09323908202472224</v>
       </c>
       <c r="C64">
-        <v>24.20003440418061</v>
+        <v>23.39140926303084</v>
       </c>
       <c r="D64">
-        <v>57.74403440418061</v>
+        <v>57.69740926303084</v>
       </c>
       <c r="E64">
-        <v>15.344</v>
+        <v>16.106</v>
       </c>
       <c r="F64">
-        <v>47.244</v>
+        <v>48.006</v>
       </c>
       <c r="G64">
         <v>13.7</v>
@@ -6523,28 +6523,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M64">
-        <v>4.25196</v>
+        <v>4.32054</v>
       </c>
       <c r="N64">
-        <v>2.898039999999999</v>
+        <v>2.829459999999998</v>
       </c>
       <c r="O64">
-        <v>0.6955295999999997</v>
+        <v>0.6790703999999995</v>
       </c>
       <c r="P64">
-        <v>2.2025104</v>
+        <v>2.150389599999999</v>
       </c>
       <c r="Q64">
-        <v>9.052510399999999</v>
+        <v>9.000389599999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1334183126005865</v>
+        <v>0.1355326541208709</v>
       </c>
       <c r="T64">
-        <v>1.801524726939924</v>
+        <v>1.844997813979979</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.681577437228948</v>
+        <v>1.654885731876108</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09323908202472224</v>
+        <v>0.09337120526122161</v>
       </c>
       <c r="C65">
-        <v>23.39140926303084</v>
+        <v>22.58285935562314</v>
       </c>
       <c r="D65">
-        <v>57.69740926303084</v>
+        <v>57.65085935562315</v>
       </c>
       <c r="E65">
-        <v>16.106</v>
+        <v>16.868</v>
       </c>
       <c r="F65">
-        <v>48.006</v>
+        <v>48.768</v>
       </c>
       <c r="G65">
         <v>13.7</v>
@@ -6605,28 +6605,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M65">
-        <v>4.32054</v>
+        <v>4.38912</v>
       </c>
       <c r="N65">
-        <v>2.829459999999998</v>
+        <v>2.760879999999998</v>
       </c>
       <c r="O65">
-        <v>0.6790703999999995</v>
+        <v>0.6626111999999996</v>
       </c>
       <c r="P65">
-        <v>2.150389599999999</v>
+        <v>2.098268799999999</v>
       </c>
       <c r="Q65">
-        <v>9.000389599999998</v>
+        <v>8.948268799999997</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1355326541208709</v>
+        <v>0.1377644590589489</v>
       </c>
       <c r="T65">
-        <v>1.844997813979979</v>
+        <v>1.890886072522261</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.654885731876108</v>
+        <v>1.629028142315543</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09337120526122161</v>
+        <v>0.093503328497721</v>
       </c>
       <c r="C66">
-        <v>22.58285935562314</v>
+        <v>21.77438450000997</v>
       </c>
       <c r="D66">
-        <v>57.65085935562315</v>
+        <v>57.60438450000998</v>
       </c>
       <c r="E66">
-        <v>16.868</v>
+        <v>17.63</v>
       </c>
       <c r="F66">
-        <v>48.768</v>
+        <v>49.53</v>
       </c>
       <c r="G66">
         <v>13.7</v>
@@ -6687,28 +6687,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M66">
-        <v>4.38912</v>
+        <v>4.4577</v>
       </c>
       <c r="N66">
-        <v>2.760879999999998</v>
+        <v>2.692299999999999</v>
       </c>
       <c r="O66">
-        <v>0.6626111999999996</v>
+        <v>0.6461519999999996</v>
       </c>
       <c r="P66">
-        <v>2.098268799999999</v>
+        <v>2.046147999999999</v>
       </c>
       <c r="Q66">
-        <v>8.948268799999997</v>
+        <v>8.896147999999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1377644590589489</v>
+        <v>0.1401237957077743</v>
       </c>
       <c r="T66">
-        <v>1.890886072522261</v>
+        <v>1.939396517266959</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.629028142315543</v>
+        <v>1.603966170895304</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.093503328497721</v>
+        <v>0.09363545173422036</v>
       </c>
       <c r="C67">
-        <v>21.77438450000997</v>
+        <v>20.96598451483005</v>
       </c>
       <c r="D67">
-        <v>57.60438450000998</v>
+        <v>57.55798451483005</v>
       </c>
       <c r="E67">
-        <v>17.63</v>
+        <v>18.392</v>
       </c>
       <c r="F67">
-        <v>49.53</v>
+        <v>50.292</v>
       </c>
       <c r="G67">
         <v>13.7</v>
@@ -6769,28 +6769,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M67">
-        <v>4.4577</v>
+        <v>4.52628</v>
       </c>
       <c r="N67">
-        <v>2.692299999999999</v>
+        <v>2.623719999999999</v>
       </c>
       <c r="O67">
-        <v>0.6461519999999996</v>
+        <v>0.6296927999999997</v>
       </c>
       <c r="P67">
-        <v>2.046147999999999</v>
+        <v>1.994027199999999</v>
       </c>
       <c r="Q67">
-        <v>8.896147999999998</v>
+        <v>8.844027199999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1401237957077743</v>
+        <v>0.142621916865354</v>
       </c>
       <c r="T67">
-        <v>1.939396517266959</v>
+        <v>1.990760517584874</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.603966170895304</v>
+        <v>1.579663653154467</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09363545173422036</v>
+        <v>0.09376757497071972</v>
       </c>
       <c r="C68">
-        <v>20.96598451483005</v>
+        <v>20.15765921930591</v>
       </c>
       <c r="D68">
-        <v>57.55798451483005</v>
+        <v>57.51165921930591</v>
       </c>
       <c r="E68">
-        <v>18.392</v>
+        <v>19.154</v>
       </c>
       <c r="F68">
-        <v>50.292</v>
+        <v>51.054</v>
       </c>
       <c r="G68">
         <v>13.7</v>
@@ -6851,28 +6851,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M68">
-        <v>4.52628</v>
+        <v>4.59486</v>
       </c>
       <c r="N68">
-        <v>2.623719999999999</v>
+        <v>2.555139999999999</v>
       </c>
       <c r="O68">
-        <v>0.6296927999999997</v>
+        <v>0.6132335999999997</v>
       </c>
       <c r="P68">
-        <v>1.994027199999999</v>
+        <v>1.941906399999999</v>
       </c>
       <c r="Q68">
-        <v>8.844027199999999</v>
+        <v>8.791906399999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.142621916865354</v>
+        <v>0.1452714393052113</v>
       </c>
       <c r="T68">
-        <v>1.990760517584874</v>
+        <v>2.045237487619026</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.579663653154467</v>
+        <v>1.5560865837044</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09376757497071972</v>
+        <v>0.09389969820721909</v>
       </c>
       <c r="C69">
-        <v>20.15765921930591</v>
+        <v>19.34940843324166</v>
       </c>
       <c r="D69">
-        <v>57.51165921930591</v>
+        <v>57.46540843324166</v>
       </c>
       <c r="E69">
-        <v>19.154</v>
+        <v>19.916</v>
       </c>
       <c r="F69">
-        <v>51.054</v>
+        <v>51.816</v>
       </c>
       <c r="G69">
         <v>13.7</v>
@@ -6933,28 +6933,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M69">
-        <v>4.59486</v>
+        <v>4.66344</v>
       </c>
       <c r="N69">
-        <v>2.555139999999999</v>
+        <v>2.486559999999998</v>
       </c>
       <c r="O69">
-        <v>0.6132335999999997</v>
+        <v>0.5967743999999995</v>
       </c>
       <c r="P69">
-        <v>1.941906399999999</v>
+        <v>1.889785599999999</v>
       </c>
       <c r="Q69">
-        <v>8.791906399999998</v>
+        <v>8.739785599999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1452714393052113</v>
+        <v>0.1480865568975597</v>
       </c>
       <c r="T69">
-        <v>2.045237487619026</v>
+        <v>2.103119268280313</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.5560865837044</v>
+        <v>1.533202957473453</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09389969820721909</v>
+        <v>0.09403182144371847</v>
       </c>
       <c r="C70">
-        <v>19.34940843324166</v>
+        <v>18.54123197702056</v>
       </c>
       <c r="D70">
-        <v>57.46540843324166</v>
+        <v>57.41923197702056</v>
       </c>
       <c r="E70">
-        <v>19.916</v>
+        <v>20.678</v>
       </c>
       <c r="F70">
-        <v>51.816</v>
+        <v>52.578</v>
       </c>
       <c r="G70">
         <v>13.7</v>
@@ -7015,28 +7015,28 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M70">
-        <v>4.66344</v>
+        <v>4.73202</v>
       </c>
       <c r="N70">
-        <v>2.486559999999998</v>
+        <v>2.417979999999998</v>
       </c>
       <c r="O70">
-        <v>0.5967743999999995</v>
+        <v>0.5803151999999996</v>
       </c>
       <c r="P70">
-        <v>1.889785599999999</v>
+        <v>1.837664799999999</v>
       </c>
       <c r="Q70">
-        <v>8.739785599999998</v>
+        <v>8.687664799999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1480865568975597</v>
+        <v>0.151083294979737</v>
       </c>
       <c r="T70">
-        <v>2.103119268280313</v>
+        <v>2.16473535737136</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.533202957473453</v>
+        <v>1.510982624756446</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09403182144371847</v>
+        <v>0.1270951927289731</v>
       </c>
       <c r="C71">
-        <v>18.54123197702056</v>
+        <v>8.166091822193756</v>
       </c>
       <c r="D71">
-        <v>57.41923197702056</v>
+        <v>47.80609182219376</v>
       </c>
       <c r="E71">
-        <v>20.678</v>
+        <v>21.44000000000001</v>
       </c>
       <c r="F71">
-        <v>52.578</v>
+        <v>53.34000000000001</v>
       </c>
       <c r="G71">
         <v>13.7</v>
@@ -7097,45 +7097,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M71">
-        <v>4.73202</v>
+        <v>7.830312000000002</v>
       </c>
       <c r="N71">
-        <v>2.417979999999998</v>
+        <v>-0.6803120000000034</v>
       </c>
       <c r="O71">
-        <v>0.5803151999999996</v>
+        <v>-0.1632748800000008</v>
       </c>
       <c r="P71">
-        <v>1.837664799999999</v>
+        <v>-0.5170371200000026</v>
       </c>
       <c r="Q71">
-        <v>8.687664799999999</v>
+        <v>6.332962879999997</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.151083294979737</v>
+        <v>0.1561829258944772</v>
       </c>
       <c r="T71">
-        <v>2.16473535737136</v>
+        <v>2.269589136432956</v>
       </c>
       <c r="U71">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.24</v>
+        <v>0.2191483557743292</v>
       </c>
       <c r="W71">
-        <v>0.0684</v>
+        <v>0.1146290213723285</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.510982624756446</v>
+        <v>0.913118149059705</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1270951927289731</v>
+        <v>0.1281051927289731</v>
       </c>
       <c r="C72">
-        <v>8.166091822193756</v>
+        <v>7.160843448790693</v>
       </c>
       <c r="D72">
-        <v>47.80609182219376</v>
+        <v>47.56284344879071</v>
       </c>
       <c r="E72">
-        <v>21.44000000000001</v>
+        <v>22.20200000000001</v>
       </c>
       <c r="F72">
-        <v>53.34000000000001</v>
+        <v>54.10200000000001</v>
       </c>
       <c r="G72">
         <v>13.7</v>
@@ -7179,37 +7179,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M72">
-        <v>7.830312000000002</v>
+        <v>7.942173600000002</v>
       </c>
       <c r="N72">
-        <v>-0.6803120000000034</v>
+        <v>-0.7921736000000035</v>
       </c>
       <c r="O72">
-        <v>-0.1632748800000008</v>
+        <v>-0.1901216640000008</v>
       </c>
       <c r="P72">
-        <v>-0.5170371200000026</v>
+        <v>-0.6020519360000026</v>
       </c>
       <c r="Q72">
-        <v>6.332962879999997</v>
+        <v>6.247948063999997</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1561829258944772</v>
+        <v>0.159989233683942</v>
       </c>
       <c r="T72">
-        <v>2.269589136432956</v>
+        <v>2.347850830792714</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2191483557743292</v>
+        <v>0.2160617592141274</v>
       </c>
       <c r="W72">
-        <v>0.1146290213723285</v>
+        <v>0.1150821337473661</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.913118149059705</v>
+        <v>0.9002573300588641</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1281051927289731</v>
+        <v>0.1291151927289731</v>
       </c>
       <c r="C73">
-        <v>7.160843448790708</v>
+        <v>6.158057950878636</v>
       </c>
       <c r="D73">
-        <v>47.56284344879071</v>
+        <v>47.32205795087863</v>
       </c>
       <c r="E73">
-        <v>22.20199999999999</v>
+        <v>22.964</v>
       </c>
       <c r="F73">
-        <v>54.102</v>
+        <v>54.864</v>
       </c>
       <c r="G73">
         <v>13.7</v>
@@ -7261,37 +7261,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M73">
-        <v>7.9421736</v>
+        <v>8.0540352</v>
       </c>
       <c r="N73">
-        <v>-0.7921736000000017</v>
+        <v>-0.9040352000000009</v>
       </c>
       <c r="O73">
-        <v>-0.1901216640000004</v>
+        <v>-0.2169684480000002</v>
       </c>
       <c r="P73">
-        <v>-0.6020519360000013</v>
+        <v>-0.6870667520000007</v>
       </c>
       <c r="Q73">
-        <v>6.247948063999998</v>
+        <v>6.162933247999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1599892336839419</v>
+        <v>0.1640674206012256</v>
       </c>
       <c r="T73">
-        <v>2.347850830792713</v>
+        <v>2.431702646178167</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2160617592141274</v>
+        <v>0.2130609014472646</v>
       </c>
       <c r="W73">
-        <v>0.1150821337473661</v>
+        <v>0.1155226596675416</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9002573300588643</v>
+        <v>0.8877537560302691</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1291151927289731</v>
+        <v>0.1301251927289731</v>
       </c>
       <c r="C74">
-        <v>6.158057950878636</v>
+        <v>5.157698112159487</v>
       </c>
       <c r="D74">
-        <v>47.32205795087863</v>
+        <v>47.08369811215948</v>
       </c>
       <c r="E74">
-        <v>22.964</v>
+        <v>23.726</v>
       </c>
       <c r="F74">
-        <v>54.864</v>
+        <v>55.626</v>
       </c>
       <c r="G74">
         <v>13.7</v>
@@ -7343,37 +7343,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M74">
-        <v>8.0540352</v>
+        <v>8.165896800000001</v>
       </c>
       <c r="N74">
-        <v>-0.9040352000000009</v>
+        <v>-1.015896800000002</v>
       </c>
       <c r="O74">
-        <v>-0.2169684480000002</v>
+        <v>-0.2438152320000005</v>
       </c>
       <c r="P74">
-        <v>-0.6870667520000007</v>
+        <v>-0.7720815680000015</v>
       </c>
       <c r="Q74">
-        <v>6.162933247999999</v>
+        <v>6.077918431999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1640674206012256</v>
+        <v>0.168447695438308</v>
       </c>
       <c r="T74">
-        <v>2.431702646178167</v>
+        <v>2.521765707147728</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2130609014472646</v>
+        <v>0.2101422589616856</v>
       </c>
       <c r="W74">
-        <v>0.1155226596675416</v>
+        <v>0.1159511163844246</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8877537560302691</v>
+        <v>0.8755927456736898</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1301251927289731</v>
+        <v>0.1311351927289731</v>
       </c>
       <c r="C75">
-        <v>5.157698112159487</v>
+        <v>4.159727462406913</v>
       </c>
       <c r="D75">
-        <v>47.08369811215948</v>
+        <v>46.84772746240691</v>
       </c>
       <c r="E75">
-        <v>23.726</v>
+        <v>24.488</v>
       </c>
       <c r="F75">
-        <v>55.626</v>
+        <v>56.388</v>
       </c>
       <c r="G75">
         <v>13.7</v>
@@ -7425,37 +7425,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M75">
-        <v>8.165896800000001</v>
+        <v>8.2777584</v>
       </c>
       <c r="N75">
-        <v>-1.015896800000002</v>
+        <v>-1.127758400000001</v>
       </c>
       <c r="O75">
-        <v>-0.2438152320000005</v>
+        <v>-0.2706620160000003</v>
       </c>
       <c r="P75">
-        <v>-0.7720815680000015</v>
+        <v>-0.8570963840000009</v>
       </c>
       <c r="Q75">
-        <v>6.077918431999998</v>
+        <v>5.992903615999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.168447695438308</v>
+        <v>0.1731649144936275</v>
       </c>
       <c r="T75">
-        <v>2.521765707147728</v>
+        <v>2.618756695884179</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2101422589616856</v>
+        <v>0.2073024987054466</v>
       </c>
       <c r="W75">
-        <v>0.1159511163844246</v>
+        <v>0.1163679931900404</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8755927456736898</v>
+        <v>0.8637604112726942</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1311351927289731</v>
+        <v>0.1321451927289731</v>
       </c>
       <c r="C76">
-        <v>4.159727462406913</v>
+        <v>3.164110258863971</v>
       </c>
       <c r="D76">
-        <v>46.84772746240691</v>
+        <v>46.61411025886397</v>
       </c>
       <c r="E76">
-        <v>24.488</v>
+        <v>25.25</v>
       </c>
       <c r="F76">
-        <v>56.388</v>
+        <v>57.15000000000001</v>
       </c>
       <c r="G76">
         <v>13.7</v>
@@ -7507,37 +7507,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M76">
-        <v>8.2777584</v>
+        <v>8.389620000000001</v>
       </c>
       <c r="N76">
-        <v>-1.127758400000001</v>
+        <v>-1.239620000000002</v>
       </c>
       <c r="O76">
-        <v>-0.2706620160000003</v>
+        <v>-0.2975088000000005</v>
       </c>
       <c r="P76">
-        <v>-0.8570963840000009</v>
+        <v>-0.9421112000000016</v>
       </c>
       <c r="Q76">
-        <v>5.992903615999999</v>
+        <v>5.907888799999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1731649144936275</v>
+        <v>0.1782595110733727</v>
       </c>
       <c r="T76">
-        <v>2.618756695884179</v>
+        <v>2.723506963719547</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2073024987054466</v>
+        <v>0.204538465389374</v>
       </c>
       <c r="W76">
-        <v>0.1163679931900404</v>
+        <v>0.1167737532808399</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8637604112726942</v>
+        <v>0.8522436057890581</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1321451927289731</v>
+        <v>0.1331551927289731</v>
       </c>
       <c r="C77">
-        <v>3.164110258863971</v>
+        <v>2.170811468194685</v>
       </c>
       <c r="D77">
-        <v>46.61411025886397</v>
+        <v>46.3828114681947</v>
       </c>
       <c r="E77">
-        <v>25.25</v>
+        <v>26.012</v>
       </c>
       <c r="F77">
-        <v>57.15000000000001</v>
+        <v>57.91200000000001</v>
       </c>
       <c r="G77">
         <v>13.7</v>
@@ -7589,37 +7589,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M77">
-        <v>8.389620000000001</v>
+        <v>8.501481600000002</v>
       </c>
       <c r="N77">
-        <v>-1.239620000000002</v>
+        <v>-1.351481600000003</v>
       </c>
       <c r="O77">
-        <v>-0.2975088000000005</v>
+        <v>-0.3243555840000008</v>
       </c>
       <c r="P77">
-        <v>-0.9421112000000016</v>
+        <v>-1.027126016000002</v>
       </c>
       <c r="Q77">
-        <v>5.907888799999998</v>
+        <v>5.822873983999997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1782595110733727</v>
+        <v>0.1837786573680965</v>
       </c>
       <c r="T77">
-        <v>2.723506963719547</v>
+        <v>2.836986420541195</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.204538465389374</v>
+        <v>0.2018471697921453</v>
       </c>
       <c r="W77">
-        <v>0.1167737532808399</v>
+        <v>0.1171688354745131</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8522436057890581</v>
+        <v>0.8410298741339388</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1331551927289731</v>
+        <v>0.1341651927289731</v>
       </c>
       <c r="C78">
-        <v>2.170811468194685</v>
+        <v>1.179796748970205</v>
       </c>
       <c r="D78">
-        <v>46.3828114681947</v>
+        <v>46.15379674897022</v>
       </c>
       <c r="E78">
-        <v>26.012</v>
+        <v>26.774</v>
       </c>
       <c r="F78">
-        <v>57.91200000000001</v>
+        <v>58.67400000000001</v>
       </c>
       <c r="G78">
         <v>13.7</v>
@@ -7671,37 +7671,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M78">
-        <v>8.501481600000002</v>
+        <v>8.613343200000001</v>
       </c>
       <c r="N78">
-        <v>-1.351481600000003</v>
+        <v>-1.463343200000002</v>
       </c>
       <c r="O78">
-        <v>-0.3243555840000008</v>
+        <v>-0.3512023680000005</v>
       </c>
       <c r="P78">
-        <v>-1.027126016000002</v>
+        <v>-1.112140832000002</v>
       </c>
       <c r="Q78">
-        <v>5.822873983999997</v>
+        <v>5.737859167999998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1837786573680965</v>
+        <v>0.189777729427579</v>
       </c>
       <c r="T78">
-        <v>2.836986420541195</v>
+        <v>2.960333656216899</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2018471697921453</v>
+        <v>0.1992257779766629</v>
       </c>
       <c r="W78">
-        <v>0.1171688354745131</v>
+        <v>0.1175536557930259</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8410298741339388</v>
+        <v>0.8301074082360955</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1341651927289731</v>
+        <v>0.1351751927289731</v>
       </c>
       <c r="C79">
-        <v>1.179796748970205</v>
+        <v>0.1910324346713281</v>
       </c>
       <c r="D79">
-        <v>46.15379674897022</v>
+        <v>45.92703243467133</v>
       </c>
       <c r="E79">
-        <v>26.774</v>
+        <v>27.536</v>
       </c>
       <c r="F79">
-        <v>58.67400000000001</v>
+        <v>59.43600000000001</v>
       </c>
       <c r="G79">
         <v>13.7</v>
@@ -7753,37 +7753,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M79">
-        <v>8.613343200000001</v>
+        <v>8.725204800000002</v>
       </c>
       <c r="N79">
-        <v>-1.463343200000002</v>
+        <v>-1.575204800000003</v>
       </c>
       <c r="O79">
-        <v>-0.3512023680000005</v>
+        <v>-0.3780491520000008</v>
       </c>
       <c r="P79">
-        <v>-1.112140832000002</v>
+        <v>-1.197155648000003</v>
       </c>
       <c r="Q79">
-        <v>5.737859167999998</v>
+        <v>5.652844351999997</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.189777729427579</v>
+        <v>0.1963221716742871</v>
       </c>
       <c r="T79">
-        <v>2.960333656216899</v>
+        <v>3.094894276954031</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1992257779766629</v>
+        <v>0.1966716013359364</v>
       </c>
       <c r="W79">
-        <v>0.1175536557930259</v>
+        <v>0.1179286089238845</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8301074082360955</v>
+        <v>0.8194650055664019</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1351751927289731</v>
+        <v>0.1361851927289731</v>
       </c>
       <c r="C80">
-        <v>0.1910324346713281</v>
+        <v>-0.7955144828104181</v>
       </c>
       <c r="D80">
-        <v>45.92703243467133</v>
+        <v>45.70248551718959</v>
       </c>
       <c r="E80">
-        <v>27.536</v>
+        <v>28.29800000000001</v>
       </c>
       <c r="F80">
-        <v>59.43600000000001</v>
+        <v>60.19800000000001</v>
       </c>
       <c r="G80">
         <v>13.7</v>
@@ -7835,37 +7835,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M80">
-        <v>8.725204800000002</v>
+        <v>8.837066400000001</v>
       </c>
       <c r="N80">
-        <v>-1.575204800000003</v>
+        <v>-1.687066400000003</v>
       </c>
       <c r="O80">
-        <v>-0.3780491520000008</v>
+        <v>-0.4048959360000006</v>
       </c>
       <c r="P80">
-        <v>-1.197155648000003</v>
+        <v>-1.282170464000002</v>
       </c>
       <c r="Q80">
-        <v>5.652844351999997</v>
+        <v>5.567829535999998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1963221716742871</v>
+        <v>0.2034898941349675</v>
       </c>
       <c r="T80">
-        <v>3.094894276954031</v>
+        <v>3.242270194904223</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1966716013359364</v>
+        <v>0.1941820873949753</v>
       </c>
       <c r="W80">
-        <v>0.1179286089238845</v>
+        <v>0.1182940695704176</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8194650055664019</v>
+        <v>0.8090920308123969</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1361851927289731</v>
+        <v>0.1820088569683835</v>
       </c>
       <c r="C81">
-        <v>-0.7955144828104181</v>
+        <v>-9.854848470668202</v>
       </c>
       <c r="D81">
-        <v>45.70248551718959</v>
+        <v>37.4051515293318</v>
       </c>
       <c r="E81">
-        <v>28.29800000000001</v>
+        <v>29.06000000000001</v>
       </c>
       <c r="F81">
-        <v>60.19800000000001</v>
+        <v>60.96000000000001</v>
       </c>
       <c r="G81">
         <v>13.7</v>
@@ -7917,45 +7917,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M81">
-        <v>8.837066400000001</v>
+        <v>12.240768</v>
       </c>
       <c r="N81">
-        <v>-1.687066400000003</v>
+        <v>-5.090768000000004</v>
       </c>
       <c r="O81">
-        <v>-0.4048959360000006</v>
+        <v>-1.221784320000001</v>
       </c>
       <c r="P81">
-        <v>-1.282170464000002</v>
+        <v>-3.868983680000003</v>
       </c>
       <c r="Q81">
-        <v>5.567829535999998</v>
+        <v>2.981016319999997</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2034898941349675</v>
+        <v>0.2194427100387678</v>
       </c>
       <c r="T81">
-        <v>3.242270194904223</v>
+        <v>3.570276880516021</v>
       </c>
       <c r="U81">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1941820873949753</v>
+        <v>0.1401872823665965</v>
       </c>
       <c r="W81">
-        <v>0.1182940695704176</v>
+        <v>0.1726503937007874</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8090920308123969</v>
+        <v>0.5841136765274857</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1820088569683835</v>
+        <v>0.1835588569683835</v>
       </c>
       <c r="C82">
-        <v>-9.854848470668202</v>
+        <v>-10.84515230132169</v>
       </c>
       <c r="D82">
-        <v>37.4051515293318</v>
+        <v>37.17684769867832</v>
       </c>
       <c r="E82">
-        <v>29.06000000000001</v>
+        <v>29.82200000000001</v>
       </c>
       <c r="F82">
-        <v>60.96000000000001</v>
+        <v>61.72200000000001</v>
       </c>
       <c r="G82">
         <v>13.7</v>
@@ -7999,37 +7999,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M82">
-        <v>12.240768</v>
+        <v>12.3937776</v>
       </c>
       <c r="N82">
-        <v>-5.090768000000004</v>
+        <v>-5.243777600000003</v>
       </c>
       <c r="O82">
-        <v>-1.221784320000001</v>
+        <v>-1.258506624000001</v>
       </c>
       <c r="P82">
-        <v>-3.868983680000003</v>
+        <v>-3.985270976000002</v>
       </c>
       <c r="Q82">
-        <v>2.981016319999997</v>
+        <v>2.864729023999997</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2194427100387678</v>
+        <v>0.2285818000408082</v>
       </c>
       <c r="T82">
-        <v>3.570276880516021</v>
+        <v>3.758186190016865</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1401872823665965</v>
+        <v>0.1384565751768855</v>
       </c>
       <c r="W82">
-        <v>0.1726503937007874</v>
+        <v>0.1729979197044814</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5841136765274857</v>
+        <v>0.5769023965703561</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1835588569683835</v>
+        <v>0.1851088569683835</v>
       </c>
       <c r="C83">
-        <v>-10.84515230132169</v>
+        <v>-11.83268611585029</v>
       </c>
       <c r="D83">
-        <v>37.17684769867832</v>
+        <v>36.95131388414972</v>
       </c>
       <c r="E83">
-        <v>29.82200000000001</v>
+        <v>30.58400000000001</v>
       </c>
       <c r="F83">
-        <v>61.72200000000001</v>
+        <v>62.48400000000001</v>
       </c>
       <c r="G83">
         <v>13.7</v>
@@ -8081,37 +8081,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M83">
-        <v>12.3937776</v>
+        <v>12.5467872</v>
       </c>
       <c r="N83">
-        <v>-5.243777600000003</v>
+        <v>-5.396787200000004</v>
       </c>
       <c r="O83">
-        <v>-1.258506624000001</v>
+        <v>-1.295228928000001</v>
       </c>
       <c r="P83">
-        <v>-3.985270976000002</v>
+        <v>-4.101558272000003</v>
       </c>
       <c r="Q83">
-        <v>2.864729023999997</v>
+        <v>2.748441727999997</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2285818000408082</v>
+        <v>0.2387363444875198</v>
       </c>
       <c r="T83">
-        <v>3.758186190016865</v>
+        <v>3.966974311684468</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1384565751768855</v>
+        <v>0.1367680803576552</v>
       </c>
       <c r="W83">
-        <v>0.1729979197044814</v>
+        <v>0.1733369694641828</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5769023965703561</v>
+        <v>0.5698670014902298</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1851088569683835</v>
+        <v>0.1866588569683835</v>
       </c>
       <c r="C84">
-        <v>-11.83268611585029</v>
+        <v>-12.81750002328005</v>
       </c>
       <c r="D84">
-        <v>36.95131388414972</v>
+        <v>36.72849997671997</v>
       </c>
       <c r="E84">
-        <v>30.58400000000001</v>
+        <v>31.34600000000001</v>
       </c>
       <c r="F84">
-        <v>62.48400000000001</v>
+        <v>63.24600000000001</v>
       </c>
       <c r="G84">
         <v>13.7</v>
@@ -8163,37 +8163,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M84">
-        <v>12.5467872</v>
+        <v>12.6997968</v>
       </c>
       <c r="N84">
-        <v>-5.396787200000004</v>
+        <v>-5.549796800000003</v>
       </c>
       <c r="O84">
-        <v>-1.295228928000001</v>
+        <v>-1.331951232000001</v>
       </c>
       <c r="P84">
-        <v>-4.101558272000003</v>
+        <v>-4.217845568000002</v>
       </c>
       <c r="Q84">
-        <v>2.748441727999997</v>
+        <v>2.632154431999997</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2387363444875198</v>
+        <v>0.2500855412220798</v>
       </c>
       <c r="T84">
-        <v>3.966974311684468</v>
+        <v>4.200325741783555</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1367680803576552</v>
+        <v>0.135120272160575</v>
       </c>
       <c r="W84">
-        <v>0.1733369694641828</v>
+        <v>0.1736678493501566</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5698670014902298</v>
+        <v>0.5630011340023958</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1866588569683835</v>
+        <v>0.1882088569683835</v>
       </c>
       <c r="C85">
-        <v>-12.81750002328005</v>
+        <v>-13.79964293126511</v>
       </c>
       <c r="D85">
-        <v>36.72849997671997</v>
+        <v>36.5083570687349</v>
       </c>
       <c r="E85">
-        <v>31.34600000000001</v>
+        <v>32.108</v>
       </c>
       <c r="F85">
-        <v>63.24600000000001</v>
+        <v>64.00800000000001</v>
       </c>
       <c r="G85">
         <v>13.7</v>
@@ -8245,37 +8245,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M85">
-        <v>12.6997968</v>
+        <v>12.8528064</v>
       </c>
       <c r="N85">
-        <v>-5.549796800000003</v>
+        <v>-5.702806400000004</v>
       </c>
       <c r="O85">
-        <v>-1.331951232000001</v>
+        <v>-1.368673536000001</v>
       </c>
       <c r="P85">
-        <v>-4.217845568000002</v>
+        <v>-4.334132864000003</v>
       </c>
       <c r="Q85">
-        <v>2.632154431999997</v>
+        <v>2.515867135999997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2500855412220798</v>
+        <v>0.2628533875484598</v>
       </c>
       <c r="T85">
-        <v>4.200325741783555</v>
+        <v>4.462846100645028</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.135120272160575</v>
+        <v>0.1335116974919967</v>
       </c>
       <c r="W85">
-        <v>0.1736678493501566</v>
+        <v>0.173990851143607</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5630011340023958</v>
+        <v>0.5562987395499863</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1882088569683835</v>
+        <v>0.1897588569683835</v>
       </c>
       <c r="C86">
-        <v>-13.79964293126508</v>
+        <v>-14.77916258187707</v>
       </c>
       <c r="D86">
-        <v>36.50835706873491</v>
+        <v>36.29083741812292</v>
       </c>
       <c r="E86">
-        <v>32.10799999999999</v>
+        <v>32.86999999999999</v>
       </c>
       <c r="F86">
-        <v>64.008</v>
+        <v>64.77</v>
       </c>
       <c r="G86">
         <v>13.7</v>
@@ -8327,37 +8327,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M86">
-        <v>12.8528064</v>
+        <v>13.005816</v>
       </c>
       <c r="N86">
-        <v>-5.7028064</v>
+        <v>-5.855816000000001</v>
       </c>
       <c r="O86">
-        <v>-1.368673536</v>
+        <v>-1.40539584</v>
       </c>
       <c r="P86">
-        <v>-4.334132864</v>
+        <v>-4.45042016</v>
       </c>
       <c r="Q86">
-        <v>2.515867136</v>
+        <v>2.399579839999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2628533875484597</v>
+        <v>0.2773236133850236</v>
       </c>
       <c r="T86">
-        <v>4.462846100645025</v>
+        <v>4.76036917402136</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1335116974919967</v>
+        <v>0.1319409716391497</v>
       </c>
       <c r="W86">
-        <v>0.173990851143607</v>
+        <v>0.1743062528948587</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5562987395499865</v>
+        <v>0.5497540484964571</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1897588569683835</v>
+        <v>0.1913088569683835</v>
       </c>
       <c r="C87">
-        <v>-14.77916258187707</v>
+        <v>-15.7561055861226</v>
       </c>
       <c r="D87">
-        <v>36.29083741812292</v>
+        <v>36.0758944138774</v>
       </c>
       <c r="E87">
-        <v>32.86999999999999</v>
+        <v>33.63199999999999</v>
       </c>
       <c r="F87">
-        <v>64.77</v>
+        <v>65.532</v>
       </c>
       <c r="G87">
         <v>13.7</v>
@@ -8409,37 +8409,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M87">
-        <v>13.005816</v>
+        <v>13.1588256</v>
       </c>
       <c r="N87">
-        <v>-5.855816000000001</v>
+        <v>-6.008825600000002</v>
       </c>
       <c r="O87">
-        <v>-1.40539584</v>
+        <v>-1.442118144</v>
       </c>
       <c r="P87">
-        <v>-4.45042016</v>
+        <v>-4.566707456000001</v>
       </c>
       <c r="Q87">
-        <v>2.399579839999999</v>
+        <v>2.283292543999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2773236133850236</v>
+        <v>0.2938610143410968</v>
       </c>
       <c r="T87">
-        <v>4.76036917402136</v>
+        <v>5.100395543594315</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1319409716391497</v>
+        <v>0.1304067742945084</v>
       </c>
       <c r="W87">
-        <v>0.1743062528948587</v>
+        <v>0.1746143197216627</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5497540484964571</v>
+        <v>0.5433615595604518</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1913088569683835</v>
+        <v>0.1928588569683835</v>
       </c>
       <c r="C88">
-        <v>-15.7561055861226</v>
+        <v>-16.73051745724126</v>
       </c>
       <c r="D88">
-        <v>36.0758944138774</v>
+        <v>35.86348254275874</v>
       </c>
       <c r="E88">
-        <v>33.63199999999999</v>
+        <v>34.39399999999999</v>
       </c>
       <c r="F88">
-        <v>65.532</v>
+        <v>66.294</v>
       </c>
       <c r="G88">
         <v>13.7</v>
@@ -8491,37 +8491,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M88">
-        <v>13.1588256</v>
+        <v>13.3118352</v>
       </c>
       <c r="N88">
-        <v>-6.008825600000002</v>
+        <v>-6.161835200000001</v>
       </c>
       <c r="O88">
-        <v>-1.442118144</v>
+        <v>-1.478840448</v>
       </c>
       <c r="P88">
-        <v>-4.566707456000001</v>
+        <v>-4.682994752000001</v>
       </c>
       <c r="Q88">
-        <v>2.283292543999998</v>
+        <v>2.167005247999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2938610143410968</v>
+        <v>0.3129426308288735</v>
       </c>
       <c r="T88">
-        <v>5.100395543594315</v>
+        <v>5.492733662332339</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1304067742945084</v>
+        <v>0.1289078458543417</v>
       </c>
       <c r="W88">
-        <v>0.1746143197216627</v>
+        <v>0.1749153045524482</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5433615595604518</v>
+        <v>0.5371160243930904</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1928588569683835</v>
+        <v>0.1944088569683835</v>
       </c>
       <c r="C89">
-        <v>-16.73051745724126</v>
+        <v>-17.70244264283443</v>
       </c>
       <c r="D89">
-        <v>35.86348254275874</v>
+        <v>35.65355735716557</v>
       </c>
       <c r="E89">
-        <v>34.39399999999999</v>
+        <v>35.15599999999999</v>
       </c>
       <c r="F89">
-        <v>66.294</v>
+        <v>67.056</v>
       </c>
       <c r="G89">
         <v>13.7</v>
@@ -8573,37 +8573,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M89">
-        <v>13.3118352</v>
+        <v>13.4648448</v>
       </c>
       <c r="N89">
-        <v>-6.161835200000001</v>
+        <v>-6.314844800000001</v>
       </c>
       <c r="O89">
-        <v>-1.478840448</v>
+        <v>-1.515562752</v>
       </c>
       <c r="P89">
-        <v>-4.682994752000001</v>
+        <v>-4.799282048000001</v>
       </c>
       <c r="Q89">
-        <v>2.167005247999999</v>
+        <v>2.050717951999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3129426308288735</v>
+        <v>0.3352045167312797</v>
       </c>
       <c r="T89">
-        <v>5.492733662332339</v>
+        <v>5.950461467526702</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1289078458543417</v>
+        <v>0.1274429839696332</v>
       </c>
       <c r="W89">
-        <v>0.1749153045524482</v>
+        <v>0.1752094488188976</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5371160243930904</v>
+        <v>0.5310124332068052</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1944088569683835</v>
+        <v>0.1959588569683835</v>
       </c>
       <c r="C90">
-        <v>-17.70244264283443</v>
+        <v>-18.6719245558719</v>
       </c>
       <c r="D90">
-        <v>35.65355735716557</v>
+        <v>35.4460754441281</v>
       </c>
       <c r="E90">
-        <v>35.15599999999999</v>
+        <v>35.91799999999999</v>
       </c>
       <c r="F90">
-        <v>67.056</v>
+        <v>67.818</v>
       </c>
       <c r="G90">
         <v>13.7</v>
@@ -8655,37 +8655,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M90">
-        <v>13.4648448</v>
+        <v>13.6178544</v>
       </c>
       <c r="N90">
-        <v>-6.314844800000001</v>
+        <v>-6.467854400000002</v>
       </c>
       <c r="O90">
-        <v>-1.515562752</v>
+        <v>-1.552285056</v>
       </c>
       <c r="P90">
-        <v>-4.799282048000001</v>
+        <v>-4.915569344000001</v>
       </c>
       <c r="Q90">
-        <v>2.050717951999999</v>
+        <v>1.934430655999998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3352045167312797</v>
+        <v>0.3615140182523051</v>
       </c>
       <c r="T90">
-        <v>5.950461467526702</v>
+        <v>6.49141251002913</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1274429839696332</v>
+        <v>0.126011040329525</v>
       </c>
       <c r="W90">
-        <v>0.1752094488188976</v>
+        <v>0.1754969831018314</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5310124332068052</v>
+        <v>0.5250460013730209</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1959588569683835</v>
+        <v>0.1975088569683835</v>
       </c>
       <c r="C91">
-        <v>-18.6719245558719</v>
+        <v>-19.63900560462247</v>
       </c>
       <c r="D91">
-        <v>35.4460754441281</v>
+        <v>35.24099439537753</v>
       </c>
       <c r="E91">
-        <v>35.91799999999999</v>
+        <v>36.67999999999999</v>
       </c>
       <c r="F91">
-        <v>67.818</v>
+        <v>68.58</v>
       </c>
       <c r="G91">
         <v>13.7</v>
@@ -8737,37 +8737,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M91">
-        <v>13.6178544</v>
+        <v>13.770864</v>
       </c>
       <c r="N91">
-        <v>-6.467854400000002</v>
+        <v>-6.620864000000001</v>
       </c>
       <c r="O91">
-        <v>-1.552285056</v>
+        <v>-1.58900736</v>
       </c>
       <c r="P91">
-        <v>-4.915569344000001</v>
+        <v>-5.031856640000001</v>
       </c>
       <c r="Q91">
-        <v>1.934430655999998</v>
+        <v>1.818143359999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3615140182523051</v>
+        <v>0.3930854200775357</v>
       </c>
       <c r="T91">
-        <v>6.49141251002913</v>
+        <v>7.140553761032042</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.126011040329525</v>
+        <v>0.124610917659197</v>
       </c>
       <c r="W91">
-        <v>0.1754969831018314</v>
+        <v>0.1757781277340333</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5250460013730209</v>
+        <v>0.5192121569133207</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1975088569683835</v>
+        <v>0.1990588569683835</v>
       </c>
       <c r="C92">
-        <v>-19.63900560462247</v>
+        <v>-20.60372722155122</v>
       </c>
       <c r="D92">
-        <v>35.24099439537753</v>
+        <v>35.03827277844877</v>
       </c>
       <c r="E92">
-        <v>36.67999999999999</v>
+        <v>37.44199999999999</v>
       </c>
       <c r="F92">
-        <v>68.58</v>
+        <v>69.342</v>
       </c>
       <c r="G92">
         <v>13.7</v>
@@ -8819,37 +8819,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M92">
-        <v>13.770864</v>
+        <v>13.9238736</v>
       </c>
       <c r="N92">
-        <v>-6.620864000000001</v>
+        <v>-6.773873600000002</v>
       </c>
       <c r="O92">
-        <v>-1.58900736</v>
+        <v>-1.625729664</v>
       </c>
       <c r="P92">
-        <v>-5.031856640000001</v>
+        <v>-5.148143936000001</v>
       </c>
       <c r="Q92">
-        <v>1.818143359999999</v>
+        <v>1.701856063999998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3930854200775357</v>
+        <v>0.4316726889750396</v>
       </c>
       <c r="T92">
-        <v>7.140553761032042</v>
+        <v>7.933948623368937</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.124610917659197</v>
+        <v>0.1232415669156893</v>
       </c>
       <c r="W92">
-        <v>0.1757781277340333</v>
+        <v>0.1760530933633296</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5192121569133207</v>
+        <v>0.5135065288153721</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1990588569683835</v>
+        <v>0.2006088569683835</v>
       </c>
       <c r="C93">
-        <v>-20.60372722155122</v>
+        <v>-21.56612989122537</v>
       </c>
       <c r="D93">
-        <v>35.03827277844877</v>
+        <v>34.83787010877463</v>
       </c>
       <c r="E93">
-        <v>37.44199999999999</v>
+        <v>38.20399999999999</v>
       </c>
       <c r="F93">
-        <v>69.342</v>
+        <v>70.104</v>
       </c>
       <c r="G93">
         <v>13.7</v>
@@ -8901,37 +8901,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M93">
-        <v>13.9238736</v>
+        <v>14.0768832</v>
       </c>
       <c r="N93">
-        <v>-6.773873600000002</v>
+        <v>-6.926883200000002</v>
       </c>
       <c r="O93">
-        <v>-1.625729664</v>
+        <v>-1.662451968000001</v>
       </c>
       <c r="P93">
-        <v>-5.148143936000001</v>
+        <v>-5.264431232000002</v>
       </c>
       <c r="Q93">
-        <v>1.701856063999998</v>
+        <v>1.585568767999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4316726889750396</v>
+        <v>0.4799067750969197</v>
       </c>
       <c r="T93">
-        <v>7.933948623368937</v>
+        <v>8.925692201290056</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1232415669156893</v>
+        <v>0.1219019846666057</v>
       </c>
       <c r="W93">
-        <v>0.1760530933633296</v>
+        <v>0.1763220814789456</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5135065288153721</v>
+        <v>0.5079249361108571</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2006088569683835</v>
+        <v>0.2021588569683835</v>
       </c>
       <c r="C94">
-        <v>-21.56612989122537</v>
+        <v>-22.52625317726765</v>
       </c>
       <c r="D94">
-        <v>34.83787010877463</v>
+        <v>34.63974682273236</v>
       </c>
       <c r="E94">
-        <v>38.20399999999999</v>
+        <v>38.96599999999999</v>
       </c>
       <c r="F94">
-        <v>70.104</v>
+        <v>70.866</v>
       </c>
       <c r="G94">
         <v>13.7</v>
@@ -8983,37 +8983,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M94">
-        <v>14.0768832</v>
+        <v>14.2298928</v>
       </c>
       <c r="N94">
-        <v>-6.926883200000002</v>
+        <v>-7.079892800000001</v>
       </c>
       <c r="O94">
-        <v>-1.662451968000001</v>
+        <v>-1.699174272</v>
       </c>
       <c r="P94">
-        <v>-5.264431232000002</v>
+        <v>-5.380718528000001</v>
       </c>
       <c r="Q94">
-        <v>1.585568767999998</v>
+        <v>1.469281471999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4799067750969197</v>
+        <v>0.541922028682194</v>
       </c>
       <c r="T94">
-        <v>8.925692201290056</v>
+        <v>10.20079108718864</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1219019846666057</v>
+        <v>0.1205912106379325</v>
       </c>
       <c r="W94">
-        <v>0.1763220814789456</v>
+        <v>0.1765852849039032</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5079249361108571</v>
+        <v>0.5024633776580523</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2021588569683835</v>
+        <v>0.2372599899798881</v>
       </c>
       <c r="C95">
-        <v>-22.52625317726765</v>
+        <v>-27.24042594480994</v>
       </c>
       <c r="D95">
-        <v>34.63974682273236</v>
+        <v>30.68757405519006</v>
       </c>
       <c r="E95">
-        <v>38.96599999999999</v>
+        <v>39.72799999999999</v>
       </c>
       <c r="F95">
-        <v>70.866</v>
+        <v>71.628</v>
       </c>
       <c r="G95">
         <v>13.7</v>
@@ -9065,45 +9065,45 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M95">
-        <v>14.2298928</v>
+        <v>16.8898824</v>
       </c>
       <c r="N95">
-        <v>-7.079892800000001</v>
+        <v>-9.739882400000003</v>
       </c>
       <c r="O95">
-        <v>-1.699174272</v>
+        <v>-2.337571776</v>
       </c>
       <c r="P95">
-        <v>-5.380718528000001</v>
+        <v>-7.402310624000002</v>
       </c>
       <c r="Q95">
-        <v>1.469281471999999</v>
+        <v>-0.5523106240000022</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.541922028682194</v>
+        <v>0.6354612503209701</v>
       </c>
       <c r="T95">
-        <v>10.20079108718864</v>
+        <v>12.12405593581848</v>
       </c>
       <c r="U95">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1205912106379325</v>
+        <v>0.1015992864461862</v>
       </c>
       <c r="W95">
-        <v>0.1765852849039032</v>
+        <v>0.2118428882559893</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.5024633776580523</v>
+        <v>0.4233303601924426</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2372599899798881</v>
+        <v>0.2391599899798881</v>
       </c>
       <c r="C96">
-        <v>-27.24042594480994</v>
+        <v>-28.19078320518677</v>
       </c>
       <c r="D96">
-        <v>30.68757405519006</v>
+        <v>30.49921679481325</v>
       </c>
       <c r="E96">
-        <v>39.72799999999999</v>
+        <v>40.49000000000001</v>
       </c>
       <c r="F96">
-        <v>71.628</v>
+        <v>72.39000000000001</v>
       </c>
       <c r="G96">
         <v>13.7</v>
@@ -9147,37 +9147,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M96">
-        <v>16.8898824</v>
+        <v>17.069562</v>
       </c>
       <c r="N96">
-        <v>-9.739882400000003</v>
+        <v>-9.919562000000006</v>
       </c>
       <c r="O96">
-        <v>-2.337571776</v>
+        <v>-2.380694880000001</v>
       </c>
       <c r="P96">
-        <v>-7.402310624000002</v>
+        <v>-7.538867120000004</v>
       </c>
       <c r="Q96">
-        <v>-0.5523106240000022</v>
+        <v>-0.6888671200000047</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6354612503209701</v>
+        <v>0.7533935003851645</v>
       </c>
       <c r="T96">
-        <v>12.12405593581848</v>
+        <v>14.54886712298218</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1015992864461862</v>
+        <v>0.1005298202730685</v>
       </c>
       <c r="W96">
-        <v>0.2118428882559893</v>
+        <v>0.2120950683796105</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4233303601924426</v>
+        <v>0.4188742511377853</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2391599899798881</v>
+        <v>0.2410599899798881</v>
       </c>
       <c r="C97">
-        <v>-28.19078320518677</v>
+        <v>-29.13884233520605</v>
       </c>
       <c r="D97">
-        <v>30.49921679481325</v>
+        <v>30.31315766479396</v>
       </c>
       <c r="E97">
-        <v>40.49000000000001</v>
+        <v>41.25200000000001</v>
       </c>
       <c r="F97">
-        <v>72.39000000000001</v>
+        <v>73.15200000000002</v>
       </c>
       <c r="G97">
         <v>13.7</v>
@@ -9229,37 +9229,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M97">
-        <v>17.069562</v>
+        <v>17.2492416</v>
       </c>
       <c r="N97">
-        <v>-9.919562000000006</v>
+        <v>-10.09924160000001</v>
       </c>
       <c r="O97">
-        <v>-2.380694880000001</v>
+        <v>-2.423817984000002</v>
       </c>
       <c r="P97">
-        <v>-7.538867120000004</v>
+        <v>-7.675423616000005</v>
       </c>
       <c r="Q97">
-        <v>-0.6888671200000047</v>
+        <v>-0.8254236160000055</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7533935003851645</v>
+        <v>0.9302918754814561</v>
       </c>
       <c r="T97">
-        <v>14.54886712298218</v>
+        <v>18.18608390372774</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1005298202730685</v>
+        <v>0.099482634645224</v>
       </c>
       <c r="W97">
-        <v>0.2120950683796105</v>
+        <v>0.2123419947506562</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4188742511377853</v>
+        <v>0.4145109776884334</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2410599899798881</v>
+        <v>0.2429599899798881</v>
       </c>
       <c r="C98">
-        <v>-29.13884233520604</v>
+        <v>-30.08464513877428</v>
       </c>
       <c r="D98">
-        <v>30.31315766479396</v>
+        <v>30.12935486122573</v>
       </c>
       <c r="E98">
-        <v>41.252</v>
+        <v>42.014</v>
       </c>
       <c r="F98">
-        <v>73.152</v>
+        <v>73.914</v>
       </c>
       <c r="G98">
         <v>13.7</v>
@@ -9311,37 +9311,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M98">
-        <v>17.2492416</v>
+        <v>17.4289212</v>
       </c>
       <c r="N98">
-        <v>-10.0992416</v>
+        <v>-10.2789212</v>
       </c>
       <c r="O98">
-        <v>-2.423817984000001</v>
+        <v>-2.466941088</v>
       </c>
       <c r="P98">
-        <v>-7.675423616000002</v>
+        <v>-7.811980112000002</v>
       </c>
       <c r="Q98">
-        <v>-0.8254236160000019</v>
+        <v>-0.9619801120000027</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9302918754814536</v>
+        <v>1.225122500641938</v>
       </c>
       <c r="T98">
-        <v>18.18608390372769</v>
+        <v>24.24811187163692</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09948263464522401</v>
+        <v>0.09845704047362377</v>
       </c>
       <c r="W98">
-        <v>0.2123419947506562</v>
+        <v>0.2125838298563195</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4145109776884335</v>
+        <v>0.410237668640099</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2429599899798881</v>
+        <v>0.2448599899798881</v>
       </c>
       <c r="C99">
-        <v>-30.08464513877428</v>
+        <v>-31.0282324120024</v>
       </c>
       <c r="D99">
-        <v>30.12935486122573</v>
+        <v>29.94776758799761</v>
       </c>
       <c r="E99">
-        <v>42.014</v>
+        <v>42.776</v>
       </c>
       <c r="F99">
-        <v>73.914</v>
+        <v>74.676</v>
       </c>
       <c r="G99">
         <v>13.7</v>
@@ -9393,37 +9393,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M99">
-        <v>17.4289212</v>
+        <v>17.6086008</v>
       </c>
       <c r="N99">
-        <v>-10.2789212</v>
+        <v>-10.4586008</v>
       </c>
       <c r="O99">
-        <v>-2.466941088</v>
+        <v>-2.510064192000001</v>
       </c>
       <c r="P99">
-        <v>-7.811980112000002</v>
+        <v>-7.948536608000002</v>
       </c>
       <c r="Q99">
-        <v>-0.9619801120000027</v>
+        <v>-1.098536608000003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.225122500641938</v>
+        <v>1.814783750962907</v>
       </c>
       <c r="T99">
-        <v>24.24811187163692</v>
+        <v>36.37216780745537</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09845704047362377</v>
+        <v>0.0974523767953215</v>
       </c>
       <c r="W99">
-        <v>0.2125838298563195</v>
+        <v>0.2128207295516632</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.410237668640099</v>
+        <v>0.4060515699805062</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2448599899798881</v>
+        <v>0.2467599899798881</v>
       </c>
       <c r="C100">
-        <v>-31.0282324120024</v>
+        <v>-31.96964397339336</v>
       </c>
       <c r="D100">
-        <v>29.94776758799761</v>
+        <v>29.76835602660664</v>
       </c>
       <c r="E100">
-        <v>42.776</v>
+        <v>43.538</v>
       </c>
       <c r="F100">
-        <v>74.676</v>
+        <v>75.438</v>
       </c>
       <c r="G100">
         <v>13.7</v>
@@ -9475,37 +9475,37 @@
         <v>7.149999999999999</v>
       </c>
       <c r="M100">
-        <v>17.6086008</v>
+        <v>17.7882804</v>
       </c>
       <c r="N100">
-        <v>-10.4586008</v>
+        <v>-10.6382804</v>
       </c>
       <c r="O100">
-        <v>-2.510064192000001</v>
+        <v>-2.553187296</v>
       </c>
       <c r="P100">
-        <v>-7.948536608000002</v>
+        <v>-8.085093104000002</v>
       </c>
       <c r="Q100">
-        <v>-1.098536608000003</v>
+        <v>-1.235093104000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.814783750962907</v>
+        <v>3.583767501925814</v>
       </c>
       <c r="T100">
-        <v>36.37216780745537</v>
+        <v>72.74433561491074</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0974523767953215</v>
+        <v>0.0964680093529445</v>
       </c>
       <c r="W100">
-        <v>0.2128207295516632</v>
+        <v>0.2130528433945757</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4060515699805062</v>
+        <v>0.4019500389706021</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2467599899798881</v>
-      </c>
-      <c r="C101">
-        <v>-31.96964397339336</v>
-      </c>
-      <c r="D101">
-        <v>29.76835602660664</v>
-      </c>
-      <c r="E101">
-        <v>43.538</v>
-      </c>
-      <c r="F101">
-        <v>75.438</v>
-      </c>
-      <c r="G101">
-        <v>13.7</v>
-      </c>
-      <c r="H101">
-        <v>44.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14</v>
-      </c>
-      <c r="K101">
-        <v>6.85</v>
-      </c>
-      <c r="L101">
-        <v>7.149999999999999</v>
-      </c>
-      <c r="M101">
-        <v>17.7882804</v>
-      </c>
-      <c r="N101">
-        <v>-10.6382804</v>
-      </c>
-      <c r="O101">
-        <v>-2.553187296</v>
-      </c>
-      <c r="P101">
-        <v>-8.085093104000002</v>
-      </c>
-      <c r="Q101">
-        <v>-1.235093104000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.583767501925814</v>
-      </c>
-      <c r="T101">
-        <v>72.74433561491074</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0964680093529445</v>
-      </c>
-      <c r="W101">
-        <v>0.2130528433945757</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4019500389706021</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
